--- a/DAGoPERT_AILV.xlsx
+++ b/DAGoPERT_AILV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djmontage\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0309663-AA25-4B2E-9B8F-5026FE2B7A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DB02FF-CC00-4F1F-BFB2-C49464A66713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="173">
   <si>
     <t>Umsetzung</t>
   </si>
@@ -1253,7 +1253,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1696,6 +1696,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1839,49 +1843,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.4322244972950713</c:v>
+                  <c:v>1.4328315577127524</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4554986782688455</c:v>
+                  <c:v>1.4558871969361618</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4645497486475356</c:v>
+                  <c:v>1.4648532788563764</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.46972178886393</c:v>
+                  <c:v>1.469976754239356</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4752170815938488</c:v>
+                  <c:v>1.4754204468337719</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4800658692967184</c:v>
+                  <c:v>1.4802237050053155</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.4887936871618839</c:v>
+                  <c:v>1.4888695697140941</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1.496875</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.504956312838116</c:v>
+                  <c:v>1.504880430285906</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5136841307032816</c:v>
+                  <c:v>1.5135262949946844</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.5185329184061511</c:v>
+                  <c:v>1.518329553166228</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5240282111360701</c:v>
+                  <c:v>1.5237732457606439</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.5292002513524643</c:v>
+                  <c:v>1.5288967211436237</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.5382513217311544</c:v>
+                  <c:v>1.5378628030638384</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.5615255027049286</c:v>
+                  <c:v>1.5609184422872475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3286,7 +3290,7 @@
       <c r="D3" s="54"/>
       <c r="E3" s="127">
         <f>SUM(E4:E10006)</f>
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F3" s="55">
         <f>SUM(F4:F10006)</f>
@@ -3294,7 +3298,7 @@
       </c>
       <c r="G3" s="55">
         <f>SUM(G4:G10006)</f>
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H3" s="56"/>
       <c r="I3" s="57">
@@ -3309,11 +3313,11 @@
       <c r="L3" s="57"/>
       <c r="M3" s="103">
         <f>N3^(1/2)</f>
-        <v>5.1720402163943007</v>
+        <v>5.123475382979799</v>
       </c>
       <c r="N3" s="121">
         <f>SUM(N4:N10006)</f>
-        <v>26.75</v>
+        <v>26.25</v>
       </c>
       <c r="O3" s="114"/>
       <c r="P3" s="59"/>
@@ -3597,19 +3601,19 @@
         <v>2</v>
       </c>
       <c r="F9" s="139">
+        <v>2.5</v>
+      </c>
+      <c r="G9" s="139">
         <v>3</v>
-      </c>
-      <c r="G9" s="139">
-        <v>4</v>
       </c>
       <c r="H9" s="131"/>
       <c r="I9" s="140">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J9" s="141">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K9" s="142">
         <v>99.73</v>
@@ -3620,11 +3624,11 @@
       </c>
       <c r="M9" s="144">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="N9" s="145">
         <f t="shared" si="3"/>
-        <v>0.1111111111111111</v>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="O9" s="146" t="str">
         <f t="shared" si="4"/>
@@ -3636,7 +3640,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="150" t="s">
         <v>145</v>
       </c>
@@ -3645,19 +3649,23 @@
       <c r="D10" s="131" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="139"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="131" t="s">
-        <v>139</v>
-      </c>
-      <c r="I10" s="140" t="str">
+      <c r="E10" s="139">
+        <v>2</v>
+      </c>
+      <c r="F10" s="139">
+        <v>2.5</v>
+      </c>
+      <c r="G10" s="139">
+        <v>3</v>
+      </c>
+      <c r="H10" s="131"/>
+      <c r="I10" s="140">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J10" s="141" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="J10" s="141">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="K10" s="142">
         <v>99.73</v>
@@ -3666,17 +3674,17 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M10" s="144" t="str">
+      <c r="M10" s="144">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N10" s="145" t="str">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N10" s="145">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="O10" s="146" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>M</v>
       </c>
       <c r="P10" s="117"/>
       <c r="Q10" s="118"/>
@@ -3691,22 +3699,22 @@
         <v>118</v>
       </c>
       <c r="E11" s="139">
+        <v>2</v>
+      </c>
+      <c r="F11" s="139">
         <v>3</v>
       </c>
-      <c r="F11" s="139">
+      <c r="G11" s="139">
         <v>4</v>
-      </c>
-      <c r="G11" s="139">
-        <v>6</v>
       </c>
       <c r="H11" s="131"/>
       <c r="I11" s="140">
         <f t="shared" si="5"/>
-        <v>4.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="J11" s="141">
         <f t="shared" si="0"/>
-        <v>4.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K11" s="142">
         <v>99.73</v>
@@ -3717,11 +3725,11 @@
       </c>
       <c r="M11" s="144">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N11" s="145">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="O11" s="146" t="str">
         <f t="shared" si="4"/>
@@ -3746,19 +3754,19 @@
         <v>3</v>
       </c>
       <c r="F12" s="139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="139">
-        <v>8</v>
-      </c>
-      <c r="H12" s="131"/>
+        <v>6</v>
+      </c>
+      <c r="H12" s="162"/>
       <c r="I12" s="140">
         <f t="shared" si="5"/>
-        <v>5.166666666666667</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="J12" s="141">
         <f t="shared" si="0"/>
-        <v>5.166666666666667</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K12" s="142">
         <v>99.73</v>
@@ -3769,11 +3777,11 @@
       </c>
       <c r="M12" s="144">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="N12" s="145">
         <f t="shared" si="3"/>
-        <v>0.69444444444444453</v>
+        <v>0.25</v>
       </c>
       <c r="O12" s="146" t="str">
         <f t="shared" si="4"/>
@@ -3801,18 +3809,18 @@
         <v>3</v>
       </c>
       <c r="G13" s="139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="131" t="s">
         <v>165</v>
       </c>
       <c r="I13" s="140">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>3.1666666666666665</v>
       </c>
       <c r="J13" s="141">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.1666666666666665</v>
       </c>
       <c r="K13" s="142">
         <v>99.73</v>
@@ -3823,11 +3831,11 @@
       </c>
       <c r="M13" s="144">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="N13" s="145">
         <f t="shared" si="3"/>
-        <v>0.1111111111111111</v>
+        <v>0.25</v>
       </c>
       <c r="O13" s="146" t="str">
         <f t="shared" si="4"/>
@@ -4911,7 +4919,7 @@
       </c>
       <c r="H34" s="131"/>
       <c r="I34" s="140">
-        <f t="shared" ref="I5:I65" si="8">IF(OR(E34="",F34="",G34=""),"",(E34+(4*F34)+G34)/6)</f>
+        <f t="shared" ref="I34:I65" si="8">IF(OR(E34="",F34="",G34=""),"",(E34+(4*F34)+G34)/6)</f>
         <v>11.833333333333334</v>
       </c>
       <c r="J34" s="141">
@@ -5924,7 +5932,7 @@
         <v>6</v>
       </c>
       <c r="M59" s="144" t="str">
-        <f t="shared" ref="M37:M68" si="14">IF(I59="","",((G59-E59)/L59)*storypoints_kalibrierung)</f>
+        <f t="shared" ref="M59:M68" si="14">IF(I59="","",((G59-E59)/L59)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N59" s="145" t="str">
@@ -8770,7 +8778,7 @@
         <v>6</v>
       </c>
       <c r="M133" s="144" t="str">
-        <f t="shared" ref="M133:M164" si="28">IF(I133="","",((G133-E133)/L133)*storypoints_kalibrierung)</f>
+        <f t="shared" ref="M133:M143" si="28">IF(I133="","",((G133-E133)/L133)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N133" s="145" t="str">
@@ -15553,19 +15561,19 @@
       </c>
       <c r="B4" s="23">
         <f>IF((Spezifikation!J3-(2*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(2*Spezifikation!M3)))</f>
-        <v>229.15591956721141</v>
+        <v>229.25304923404039</v>
       </c>
       <c r="C4" s="18">
         <f>IF(B4="NV",C5,B4/Einstellungen!$B$53)</f>
-        <v>28.644489945901427</v>
+        <v>28.656631154255049</v>
       </c>
       <c r="D4" s="18">
         <f>IF(B4="NV",D5,B4/Einstellungen!$B$54)</f>
-        <v>1.4322244972950713</v>
+        <v>1.4328315577127524</v>
       </c>
       <c r="E4" s="6">
         <f>IF(B4="NV",E5,B4/Einstellungen!$B$55)</f>
-        <v>0.11935204144125594</v>
+        <v>0.11940262980939603</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -15574,19 +15582,19 @@
       </c>
       <c r="B5" s="23">
         <f>IF((Spezifikation!J3-(1.28*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1.28*Spezifikation!M3)))</f>
-        <v>232.87978852301529</v>
+        <v>232.94195150978587</v>
       </c>
       <c r="C5" s="18">
         <f>IF(B5="NV",C6,B5/Einstellungen!$B$53)</f>
-        <v>29.109973565376912</v>
+        <v>29.117743938723233</v>
       </c>
       <c r="D5" s="18">
         <f>IF(B5="NV",D6,B5/Einstellungen!$B$54)</f>
-        <v>1.4554986782688455</v>
+        <v>1.4558871969361618</v>
       </c>
       <c r="E5" s="6">
         <f>IF(B5="NV",E6,B5/Einstellungen!$B$55)</f>
-        <v>0.1212915565224038</v>
+        <v>0.12132393307801347</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -15595,19 +15603,19 @@
       </c>
       <c r="B6" s="18">
         <f>IF((Spezifikation!J3-(1*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1*Spezifikation!M3)))</f>
-        <v>234.32795978360571</v>
+        <v>234.37652461702021</v>
       </c>
       <c r="C6" s="18">
         <f>IF(B6="NV",C7,B6/Einstellungen!$B$53)</f>
-        <v>29.290994972950713</v>
+        <v>29.297065577127526</v>
       </c>
       <c r="D6" s="18">
         <f>IF(B6="NV",D7,B6/Einstellungen!$B$54)</f>
-        <v>1.4645497486475356</v>
+        <v>1.4648532788563764</v>
       </c>
       <c r="E6" s="6">
         <f>IF(B6="NV",E7,B6/Einstellungen!$B$55)</f>
-        <v>0.12204581238729464</v>
+        <v>0.12207110657136469</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -15616,19 +15624,19 @@
       </c>
       <c r="B7" s="18">
         <f>IF((Spezifikation!J3-(0.84*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.84*Spezifikation!M3)))</f>
-        <v>235.15548621822879</v>
+        <v>235.19628067829697</v>
       </c>
       <c r="C7" s="18">
         <f>IF(B7="NV",C8,B7/Einstellungen!$B$53)</f>
-        <v>29.394435777278598</v>
+        <v>29.399535084787122</v>
       </c>
       <c r="D7" s="18">
         <f>IF(B7="NV",D8,B7/Einstellungen!$B$54)</f>
-        <v>1.46972178886393</v>
+        <v>1.469976754239356</v>
       </c>
       <c r="E7" s="6">
         <f>IF(B7="NV",E8,B7/Einstellungen!$B$55)</f>
-        <v>0.12247681573866083</v>
+        <v>0.12249806285327967</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -15637,19 +15645,19 @@
       </c>
       <c r="B8" s="22">
         <f>IF((Spezifikation!J3-(0.67*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.67*Spezifikation!M3)))</f>
-        <v>236.03473305501581</v>
+        <v>236.06727149340352</v>
       </c>
       <c r="C8" s="22">
         <f>IF(B8="NV",C9,B8/Einstellungen!$B$53)</f>
-        <v>29.504341631876976</v>
+        <v>29.508408936675441</v>
       </c>
       <c r="D8" s="22">
         <f>IF(B8="NV",D9,B8/Einstellungen!$B$54)</f>
-        <v>1.4752170815938488</v>
+        <v>1.4754204468337719</v>
       </c>
       <c r="E8" s="22">
         <f>IF(B8="NV",E9,B8/Einstellungen!$B$55)</f>
-        <v>0.1229347567994874</v>
+        <v>0.12295170390281433</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -15658,19 +15666,19 @@
       </c>
       <c r="B9" s="18">
         <f>IF((Spezifikation!J3-(0.52*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.52*Spezifikation!M3)))</f>
-        <v>236.81053908747495</v>
+        <v>236.8357928008505</v>
       </c>
       <c r="C9" s="18">
         <f>IF(B9="NV",C10,B9/Einstellungen!$B$53)</f>
-        <v>29.601317385934369</v>
+        <v>29.604474100106312</v>
       </c>
       <c r="D9" s="18">
         <f>IF(B9="NV",D10,B9/Einstellungen!$B$54)</f>
-        <v>1.4800658692967184</v>
+        <v>1.4802237050053155</v>
       </c>
       <c r="E9" s="6">
         <f>IF(B9="NV",E10,B9/Einstellungen!$B$55)</f>
-        <v>0.1233388224413932</v>
+        <v>0.12335197541710964</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -15679,19 +15687,19 @@
       </c>
       <c r="B10" s="18">
         <f>IF((Spezifikation!J3-(0.25*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.25*Spezifikation!M3)))</f>
-        <v>238.20698994590143</v>
+        <v>238.21913115425505</v>
       </c>
       <c r="C10" s="18">
         <f>IF(B10="NV",C11,B10/Einstellungen!$B$53)</f>
-        <v>29.775873743237678</v>
+        <v>29.777391394281882</v>
       </c>
       <c r="D10" s="18">
         <f>IF(B10="NV",D11,B10/Einstellungen!$B$54)</f>
-        <v>1.4887936871618839</v>
+        <v>1.4888695697140941</v>
       </c>
       <c r="E10" s="6">
         <f>IF(B10="NV",E11,B10/Einstellungen!$B$55)</f>
-        <v>0.12406614059682367</v>
+        <v>0.12407246414284118</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -15721,19 +15729,19 @@
       </c>
       <c r="B12" s="18">
         <f>Spezifikation!J3+(0.25*Spezifikation!M3)</f>
-        <v>240.79301005409857</v>
+        <v>240.78086884574495</v>
       </c>
       <c r="C12" s="18">
         <f>B12/Einstellungen!B53</f>
-        <v>30.099126256762322</v>
+        <v>30.097608605718118</v>
       </c>
       <c r="D12" s="18">
         <f>B12/Einstellungen!B54</f>
-        <v>1.504956312838116</v>
+        <v>1.504880430285906</v>
       </c>
       <c r="E12" s="6">
         <f>B12/Einstellungen!B55</f>
-        <v>0.125413026069843</v>
+        <v>0.12540670252382549</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -15742,19 +15750,19 @@
       </c>
       <c r="B13" s="18">
         <f>Spezifikation!J3+(0.52*Spezifikation!M3)</f>
-        <v>242.18946091252505</v>
+        <v>242.1642071991495</v>
       </c>
       <c r="C13" s="18">
         <f>B13/Einstellungen!B53</f>
-        <v>30.273682614065631</v>
+        <v>30.270525899893688</v>
       </c>
       <c r="D13" s="18">
         <f>B13/Einstellungen!B54</f>
-        <v>1.5136841307032816</v>
+        <v>1.5135262949946844</v>
       </c>
       <c r="E13" s="6">
         <f>B13/Einstellungen!B55</f>
-        <v>0.12614034422527345</v>
+        <v>0.12612719124955704</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -15763,19 +15771,19 @@
       </c>
       <c r="B14" s="22">
         <f>Spezifikation!J3+(0.67*Spezifikation!M3)</f>
-        <v>242.96526694498419</v>
+        <v>242.93272850659648</v>
       </c>
       <c r="C14" s="22">
         <f>B14/Einstellungen!B53</f>
-        <v>30.370658368123024</v>
+        <v>30.366591063324559</v>
       </c>
       <c r="D14" s="22">
         <f>B14/Einstellungen!B54</f>
-        <v>1.5185329184061511</v>
+        <v>1.518329553166228</v>
       </c>
       <c r="E14" s="135">
         <f>B14/Einstellungen!B55</f>
-        <v>0.12654440986717927</v>
+        <v>0.12652746276385232</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -15784,19 +15792,19 @@
       </c>
       <c r="B15" s="18">
         <f>Spezifikation!J3+(0.84*Spezifikation!M3)</f>
-        <v>243.84451378177121</v>
+        <v>243.80371932170303</v>
       </c>
       <c r="C15" s="18">
         <f>B15/Einstellungen!B53</f>
-        <v>30.480564222721402</v>
+        <v>30.475464915212878</v>
       </c>
       <c r="D15" s="18">
         <f>B15/Einstellungen!B54</f>
-        <v>1.5240282111360701</v>
+        <v>1.5237732457606439</v>
       </c>
       <c r="E15" s="6">
         <f>B15/Einstellungen!B55</f>
-        <v>0.12700235092800585</v>
+        <v>0.12698110381338698</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -15805,19 +15813,19 @@
       </c>
       <c r="B16" s="18">
         <f>Spezifikation!J3+(1*Spezifikation!M3)</f>
-        <v>244.67204021639429</v>
+        <v>244.62347538297979</v>
       </c>
       <c r="C16" s="18">
         <f>B16/Einstellungen!B53</f>
-        <v>30.584005027049287</v>
+        <v>30.577934422872474</v>
       </c>
       <c r="D16" s="18">
         <f>B16/Einstellungen!B54</f>
-        <v>1.5292002513524643</v>
+        <v>1.5288967211436237</v>
       </c>
       <c r="E16" s="6">
         <f>B16/Einstellungen!B55</f>
-        <v>0.12743335427937202</v>
+        <v>0.12740806009530198</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -15826,19 +15834,19 @@
       </c>
       <c r="B17" s="18">
         <f>Spezifikation!J3+(1.28*Spezifikation!M3)</f>
-        <v>246.12021147698471</v>
+        <v>246.05804849021413</v>
       </c>
       <c r="C17" s="18">
         <f>B17/Einstellungen!B53</f>
-        <v>30.765026434623088</v>
+        <v>30.757256061276767</v>
       </c>
       <c r="D17" s="18">
         <f>B17/Einstellungen!B54</f>
-        <v>1.5382513217311544</v>
+        <v>1.5378628030638384</v>
       </c>
       <c r="E17" s="6">
         <f>B17/Einstellungen!B55</f>
-        <v>0.12818761014426286</v>
+        <v>0.12815523358865319</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -15847,19 +15855,19 @@
       </c>
       <c r="B18" s="26">
         <f>Spezifikation!J3+(2*Spezifikation!M3)</f>
-        <v>249.84408043278859</v>
+        <v>249.74695076595961</v>
       </c>
       <c r="C18" s="26">
         <f>B18/Einstellungen!B53</f>
-        <v>31.230510054098573</v>
+        <v>31.218368845744951</v>
       </c>
       <c r="D18" s="26">
         <f>B18/Einstellungen!B54</f>
-        <v>1.5615255027049286</v>
+        <v>1.5609184422872475</v>
       </c>
       <c r="E18" s="136">
         <f>B18/Einstellungen!B55</f>
-        <v>0.13012712522541073</v>
+        <v>0.13007653685727064</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15996,7 +16004,7 @@
       </c>
       <c r="C14" s="32">
         <f>Aufwandschätzung!B8</f>
-        <v>236.03473305501581</v>
+        <v>236.06727149340352</v>
       </c>
       <c r="D14" s="32">
         <f>Aufwandschätzung!B11</f>
@@ -16004,11 +16012,11 @@
       </c>
       <c r="E14" s="32">
         <f>Aufwandschätzung!B14</f>
-        <v>242.96526694498419</v>
+        <v>242.93272850659648</v>
       </c>
       <c r="F14" s="33">
         <f>Aufwandschätzung!B18</f>
-        <v>249.84408043278859</v>
+        <v>249.74695076595961</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -16017,7 +16025,7 @@
       </c>
       <c r="C15" s="34">
         <f>C14/C6</f>
-        <v>30.653861435716337</v>
+        <v>30.658087206935523</v>
       </c>
       <c r="D15" s="34">
         <f>D14/C6</f>
@@ -16025,11 +16033,11 @@
       </c>
       <c r="E15" s="34">
         <f>E14/C6</f>
-        <v>31.553930772075869</v>
+        <v>31.549705000856683</v>
       </c>
       <c r="F15" s="35">
         <f>F14/C6</f>
-        <v>32.447283173089424</v>
+        <v>32.434668930644108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -16079,7 +16087,7 @@
       </c>
       <c r="C19" s="38">
         <f>(C5*C14)+C16+C17</f>
-        <v>32808.827894647198</v>
+        <v>32813.350737583089</v>
       </c>
       <c r="D19" s="38">
         <f>(C5*D14)+D16+D17</f>
@@ -16087,11 +16095,11 @@
       </c>
       <c r="E19" s="38">
         <f>(C5*E14)+E16+E17</f>
-        <v>33772.172105352802</v>
+        <v>33767.649262416911</v>
       </c>
       <c r="F19" s="40">
         <f>(C5*F14)+F16+F17</f>
-        <v>34728.327180157612</v>
+        <v>34714.826156468385</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -16953,6 +16961,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100CA39AF47FDE84445B2A1A204EB607015" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="02d257b5fc73ffec8ca48af1d6f0ac4f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="025d22c0-f634-4698-b91b-a929f7363a0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9eef9cb57a7ecff21c60d28da668db25" ns2:_="">
     <xsd:import namespace="025d22c0-f634-4698-b91b-a929f7363a0d"/>
@@ -17130,22 +17153,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90C8B9A1-CF49-4753-98D3-CDFF9713AD0B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="025d22c0-f634-4698-b91b-a929f7363a0d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F155915-390F-4DB1-8323-6D9C71B4FD2C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68C4F521-E81F-4050-A011-79AAC4B11AEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17161,28 +17193,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F155915-390F-4DB1-8323-6D9C71B4FD2C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90C8B9A1-CF49-4753-98D3-CDFF9713AD0B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="025d22c0-f634-4698-b91b-a929f7363a0d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DAGoPERT_AILV.xlsx
+++ b/DAGoPERT_AILV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elena\Desktop\FH\INNO\AILV-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F1B624-EE21-4850-B8C4-00423438D11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75581E5C-1CF3-4858-84EF-48E6C2E81B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="636" yWindow="3360" windowWidth="22404" windowHeight="8880" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="18" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="172">
   <si>
     <t>Umsetzung</t>
   </si>
@@ -512,9 +512,6 @@
   </si>
   <si>
     <t>1.5</t>
-  </si>
-  <si>
-    <t>Aufgrund der fehlenden Erfahrung, wird die Schätzung vorerst ausgelassen</t>
   </si>
   <si>
     <t>2.1</t>
@@ -1843,49 +1840,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.4828622159501934</c:v>
+                  <c:v>1.5448548269923559</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5074068182081237</c:v>
+                  <c:v>1.5695820892751076</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.51695194130843</c:v>
+                  <c:v>1.5791982468295112</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5224062973657477</c:v>
+                  <c:v>1.5846931940034561</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.528201550676648</c:v>
+                  <c:v>1.5905315753757725</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5333150094803836</c:v>
+                  <c:v>1.5956830883513455</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5425192353271073</c:v>
+                  <c:v>1.6049558117073777</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.5510416666666667</c:v>
+                  <c:v>1.6135416666666664</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5595640980062258</c:v>
+                  <c:v>1.6221275216259552</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5687683238529497</c:v>
+                  <c:v>1.6314002449819871</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.5738817826566851</c:v>
+                  <c:v>1.6365517579575606</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5796770359675854</c:v>
+                  <c:v>1.642390139329877</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.5851313920249033</c:v>
+                  <c:v>1.6478850865038219</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.5946765151252094</c:v>
+                  <c:v>1.6575012440582253</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.6192211173831399</c:v>
+                  <c:v>1.682228506340977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3290,34 +3287,34 @@
       <c r="D3" s="54"/>
       <c r="E3" s="127">
         <f>SUM(E4:E10006)</f>
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F3" s="55">
         <f>SUM(F4:F10006)</f>
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G3" s="55">
         <f>SUM(G4:G10006)</f>
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="H3" s="56"/>
       <c r="I3" s="57">
         <f>SUM(I4:I10006)</f>
-        <v>248.16666666666666</v>
+        <v>258.16666666666663</v>
       </c>
       <c r="J3" s="58">
         <f>SUM(J4:J10006)</f>
-        <v>248.16666666666666</v>
+        <v>258.16666666666663</v>
       </c>
       <c r="K3" s="57"/>
       <c r="L3" s="57"/>
       <c r="M3" s="103">
         <f>N3^(1/2)</f>
-        <v>5.4543560573178569</v>
+        <v>5.494947173944845</v>
       </c>
       <c r="N3" s="121">
         <f>SUM(N4:N10006)</f>
-        <v>29.749999999999996</v>
+        <v>30.194444444444439</v>
       </c>
       <c r="O3" s="114"/>
       <c r="P3" s="59"/>
@@ -3586,7 +3583,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="150" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B9" s="131" t="s">
         <v>93</v>
@@ -3642,7 +3639,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="150" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B10" s="131"/>
       <c r="C10" s="131"/>
@@ -3691,7 +3688,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="150" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B11" s="131"/>
       <c r="C11" s="131"/>
@@ -3743,7 +3740,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="150" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="131"/>
       <c r="C12" s="131"/>
@@ -3795,7 +3792,7 @@
     </row>
     <row r="13" spans="1:17" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A13" s="150" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B13" s="131"/>
       <c r="C13" s="131"/>
@@ -3812,7 +3809,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="131" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I13" s="140">
         <f t="shared" si="5"/>
@@ -3849,7 +3846,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" s="131" t="s">
         <v>95</v>
@@ -3905,7 +3902,7 @@
     </row>
     <row r="15" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A15" s="150" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B15" s="131"/>
       <c r="C15" s="131"/>
@@ -3922,7 +3919,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="151" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I15" s="140">
         <f t="shared" si="5"/>
@@ -4011,12 +4008,12 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="150" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B17" s="131"/>
       <c r="C17" s="131"/>
       <c r="D17" s="131" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E17" s="139">
         <v>3</v>
@@ -4060,7 +4057,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="150" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" s="131"/>
       <c r="C18" s="131"/>
@@ -4112,12 +4109,12 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="150" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B19" s="131"/>
       <c r="C19" s="131"/>
       <c r="D19" s="131" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E19" s="139">
         <v>3</v>
@@ -4161,26 +4158,30 @@
     </row>
     <row r="20" spans="1:17" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="150" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B20" s="131"/>
       <c r="C20" s="131"/>
       <c r="D20" s="131" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="131" t="s">
-        <v>139</v>
-      </c>
-      <c r="I20" s="140" t="str">
+      <c r="E20" s="139">
+        <v>8</v>
+      </c>
+      <c r="F20" s="139">
+        <v>10</v>
+      </c>
+      <c r="G20" s="139">
+        <v>12</v>
+      </c>
+      <c r="H20" s="131"/>
+      <c r="I20" s="140">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J20" s="141" t="str">
+        <v>10</v>
+      </c>
+      <c r="J20" s="141">
         <f t="shared" si="0"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K20" s="142">
         <v>99.73</v>
@@ -4189,17 +4190,17 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M20" s="144" t="str">
+      <c r="M20" s="144">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N20" s="145" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N20" s="145">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.44444444444444442</v>
       </c>
       <c r="O20" s="146" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="P20" s="117"/>
       <c r="Q20" s="118" t="str">
@@ -4209,7 +4210,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="150" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" s="131" t="s">
         <v>92</v>
@@ -4265,7 +4266,7 @@
     </row>
     <row r="22" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A22" s="150" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B22" s="131"/>
       <c r="C22" s="131"/>
@@ -4317,7 +4318,7 @@
     </row>
     <row r="23" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A23" s="150" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B23" s="147" t="s">
         <v>121</v>
@@ -4373,7 +4374,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B24" s="131"/>
       <c r="C24" s="131"/>
@@ -4425,7 +4426,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B25" s="131"/>
       <c r="C25" s="131" t="s">
@@ -4479,7 +4480,7 @@
     </row>
     <row r="26" spans="1:17" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="150" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B26" s="131" t="s">
         <v>125</v>
@@ -4535,7 +4536,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="150" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B27" s="131"/>
       <c r="C27" s="131"/>
@@ -4587,7 +4588,7 @@
     </row>
     <row r="28" spans="1:17" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A28" s="150" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B28" s="131"/>
       <c r="C28" s="148" t="s">
@@ -4641,7 +4642,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="150" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" s="131"/>
       <c r="C29" s="131"/>
@@ -4693,7 +4694,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="150" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B30" s="131"/>
       <c r="C30" s="131"/>
@@ -4745,7 +4746,7 @@
     </row>
     <row r="31" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A31" s="150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="147" t="s">
         <v>126</v>
@@ -4801,7 +4802,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="150" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B32" s="147"/>
       <c r="C32" s="131"/>
@@ -4850,7 +4851,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="150" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B33" s="147"/>
       <c r="C33" s="131" t="s">
@@ -4901,7 +4902,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="150" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B34" s="131"/>
       <c r="C34" s="131"/>
@@ -4953,12 +4954,12 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="150" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B35" s="131"/>
       <c r="C35" s="131"/>
       <c r="D35" s="131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E35" s="139">
         <v>15</v>
@@ -5005,11 +5006,11 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="150" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B36" s="131"/>
       <c r="D36" s="51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E36" s="139">
         <v>2</v>
@@ -15561,19 +15562,19 @@
       </c>
       <c r="B4" s="23">
         <f>IF((Spezifikation!J3-(2*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(2*Spezifikation!M3)))</f>
-        <v>237.25795455203095</v>
+        <v>247.17677231877693</v>
       </c>
       <c r="C4" s="18">
         <f>IF(B4="NV",C5,B4/Einstellungen!$B$53)</f>
-        <v>29.657244319003869</v>
+        <v>30.897096539847116</v>
       </c>
       <c r="D4" s="18">
         <f>IF(B4="NV",D5,B4/Einstellungen!$B$54)</f>
-        <v>1.4828622159501934</v>
+        <v>1.5448548269923559</v>
       </c>
       <c r="E4" s="6">
         <f>IF(B4="NV",E5,B4/Einstellungen!$B$55)</f>
-        <v>0.12357185132918279</v>
+        <v>0.12873790224936299</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -15582,19 +15583,19 @@
       </c>
       <c r="B5" s="23">
         <f>IF((Spezifikation!J3-(1.28*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1.28*Spezifikation!M3)))</f>
-        <v>241.1850909132998</v>
+        <v>251.13313428401722</v>
       </c>
       <c r="C5" s="18">
         <f>IF(B5="NV",C6,B5/Einstellungen!$B$53)</f>
-        <v>30.148136364162475</v>
+        <v>31.391641785502152</v>
       </c>
       <c r="D5" s="18">
         <f>IF(B5="NV",D6,B5/Einstellungen!$B$54)</f>
-        <v>1.5074068182081237</v>
+        <v>1.5695820892751076</v>
       </c>
       <c r="E5" s="6">
         <f>IF(B5="NV",E6,B5/Einstellungen!$B$55)</f>
-        <v>0.12561723485067697</v>
+        <v>0.13079850743959229</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -15603,19 +15604,19 @@
       </c>
       <c r="B6" s="18">
         <f>IF((Spezifikation!J3-(1*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1*Spezifikation!M3)))</f>
-        <v>242.7123106093488</v>
+        <v>252.67171949272179</v>
       </c>
       <c r="C6" s="18">
         <f>IF(B6="NV",C7,B6/Einstellungen!$B$53)</f>
-        <v>30.339038826168601</v>
+        <v>31.583964936590224</v>
       </c>
       <c r="D6" s="18">
         <f>IF(B6="NV",D7,B6/Einstellungen!$B$54)</f>
-        <v>1.51695194130843</v>
+        <v>1.5791982468295112</v>
       </c>
       <c r="E6" s="6">
         <f>IF(B6="NV",E7,B6/Einstellungen!$B$55)</f>
-        <v>0.12641266177570251</v>
+        <v>0.13159985390245926</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -15624,19 +15625,19 @@
       </c>
       <c r="B7" s="18">
         <f>IF((Spezifikation!J3-(0.84*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.84*Spezifikation!M3)))</f>
-        <v>243.58500757851965</v>
+        <v>253.55091104055296</v>
       </c>
       <c r="C7" s="18">
         <f>IF(B7="NV",C8,B7/Einstellungen!$B$53)</f>
-        <v>30.448125947314956</v>
+        <v>31.69386388006912</v>
       </c>
       <c r="D7" s="18">
         <f>IF(B7="NV",D8,B7/Einstellungen!$B$54)</f>
-        <v>1.5224062973657477</v>
+        <v>1.5846931940034561</v>
       </c>
       <c r="E7" s="6">
         <f>IF(B7="NV",E8,B7/Einstellungen!$B$55)</f>
-        <v>0.12686719144714564</v>
+        <v>0.13205776616695467</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -15645,19 +15646,19 @@
       </c>
       <c r="B8" s="22">
         <f>IF((Spezifikation!J3-(0.67*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.67*Spezifikation!M3)))</f>
-        <v>244.51224810826369</v>
+        <v>254.48505206012359</v>
       </c>
       <c r="C8" s="22">
         <f>IF(B8="NV",C9,B8/Einstellungen!$B$53)</f>
-        <v>30.564031013532961</v>
+        <v>31.810631507515449</v>
       </c>
       <c r="D8" s="22">
         <f>IF(B8="NV",D9,B8/Einstellungen!$B$54)</f>
-        <v>1.528201550676648</v>
+        <v>1.5905315753757725</v>
       </c>
       <c r="E8" s="22">
         <f>IF(B8="NV",E9,B8/Einstellungen!$B$55)</f>
-        <v>0.127350129223054</v>
+        <v>0.13254429794798103</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -15666,19 +15667,19 @@
       </c>
       <c r="B9" s="18">
         <f>IF((Spezifikation!J3-(0.52*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.52*Spezifikation!M3)))</f>
-        <v>245.33040151686137</v>
+        <v>255.3092941362153</v>
       </c>
       <c r="C9" s="18">
         <f>IF(B9="NV",C10,B9/Einstellungen!$B$53)</f>
-        <v>30.666300189607671</v>
+        <v>31.913661767026912</v>
       </c>
       <c r="D9" s="18">
         <f>IF(B9="NV",D10,B9/Einstellungen!$B$54)</f>
-        <v>1.5333150094803836</v>
+        <v>1.5956830883513455</v>
       </c>
       <c r="E9" s="6">
         <f>IF(B9="NV",E10,B9/Einstellungen!$B$55)</f>
-        <v>0.12777625079003196</v>
+        <v>0.13297359069594547</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -15687,19 +15688,19 @@
       </c>
       <c r="B10" s="18">
         <f>IF((Spezifikation!J3-(0.25*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.25*Spezifikation!M3)))</f>
-        <v>246.80307765233718</v>
+        <v>256.79292987318041</v>
       </c>
       <c r="C10" s="18">
         <f>IF(B10="NV",C11,B10/Einstellungen!$B$53)</f>
-        <v>30.850384706542147</v>
+        <v>32.099116234147552</v>
       </c>
       <c r="D10" s="18">
         <f>IF(B10="NV",D11,B10/Einstellungen!$B$54)</f>
-        <v>1.5425192353271073</v>
+        <v>1.6049558117073777</v>
       </c>
       <c r="E10" s="6">
         <f>IF(B10="NV",E11,B10/Einstellungen!$B$55)</f>
-        <v>0.12854326961059229</v>
+        <v>0.13374631764228145</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -15708,19 +15709,19 @@
       </c>
       <c r="B11" s="22">
         <f>Spezifikation!J3</f>
-        <v>248.16666666666666</v>
+        <v>258.16666666666663</v>
       </c>
       <c r="C11" s="22">
         <f>B11/Einstellungen!B53</f>
-        <v>31.020833333333332</v>
+        <v>32.270833333333329</v>
       </c>
       <c r="D11" s="22">
         <f>B11/Einstellungen!B54</f>
-        <v>1.5510416666666667</v>
+        <v>1.6135416666666664</v>
       </c>
       <c r="E11" s="135">
         <f>B11/Einstellungen!B55</f>
-        <v>0.12925347222222222</v>
+        <v>0.13446180555555554</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -15729,19 +15730,19 @@
       </c>
       <c r="B12" s="18">
         <f>Spezifikation!J3+(0.25*Spezifikation!M3)</f>
-        <v>249.53025568099613</v>
+        <v>259.54040346015285</v>
       </c>
       <c r="C12" s="18">
         <f>B12/Einstellungen!B53</f>
-        <v>31.191281960124517</v>
+        <v>32.442550432519106</v>
       </c>
       <c r="D12" s="18">
         <f>B12/Einstellungen!B54</f>
-        <v>1.5595640980062258</v>
+        <v>1.6221275216259552</v>
       </c>
       <c r="E12" s="6">
         <f>B12/Einstellungen!B55</f>
-        <v>0.12996367483385216</v>
+        <v>0.13517729346882962</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -15750,19 +15751,19 @@
       </c>
       <c r="B13" s="18">
         <f>Spezifikation!J3+(0.52*Spezifikation!M3)</f>
-        <v>251.00293181647194</v>
+        <v>261.02403919711793</v>
       </c>
       <c r="C13" s="18">
         <f>B13/Einstellungen!B53</f>
-        <v>31.375366477058993</v>
+        <v>32.628004899639741</v>
       </c>
       <c r="D13" s="18">
         <f>B13/Einstellungen!B54</f>
-        <v>1.5687683238529497</v>
+        <v>1.6314002449819871</v>
       </c>
       <c r="E13" s="6">
         <f>B13/Einstellungen!B55</f>
-        <v>0.13073069365441248</v>
+        <v>0.1359500204151656</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -15771,19 +15772,19 @@
       </c>
       <c r="B14" s="22">
         <f>Spezifikation!J3+(0.67*Spezifikation!M3)</f>
-        <v>251.82108522506962</v>
+        <v>261.84828127320969</v>
       </c>
       <c r="C14" s="22">
         <f>B14/Einstellungen!B53</f>
-        <v>31.477635653133703</v>
+        <v>32.731035159151212</v>
       </c>
       <c r="D14" s="22">
         <f>B14/Einstellungen!B54</f>
-        <v>1.5738817826566851</v>
+        <v>1.6365517579575606</v>
       </c>
       <c r="E14" s="135">
         <f>B14/Einstellungen!B55</f>
-        <v>0.13115681522139042</v>
+        <v>0.13637931316313004</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -15792,19 +15793,19 @@
       </c>
       <c r="B15" s="18">
         <f>Spezifikation!J3+(0.84*Spezifikation!M3)</f>
-        <v>252.74832575481366</v>
+        <v>262.78242229278032</v>
       </c>
       <c r="C15" s="18">
         <f>B15/Einstellungen!B53</f>
-        <v>31.593540719351708</v>
+        <v>32.847802786597541</v>
       </c>
       <c r="D15" s="18">
         <f>B15/Einstellungen!B54</f>
-        <v>1.5796770359675854</v>
+        <v>1.642390139329877</v>
       </c>
       <c r="E15" s="6">
         <f>B15/Einstellungen!B55</f>
-        <v>0.13163975299729877</v>
+        <v>0.13686584494415641</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -15813,19 +15814,19 @@
       </c>
       <c r="B16" s="18">
         <f>Spezifikation!J3+(1*Spezifikation!M3)</f>
-        <v>253.62102272398451</v>
+        <v>263.66161384061149</v>
       </c>
       <c r="C16" s="18">
         <f>B16/Einstellungen!B53</f>
-        <v>31.702627840498064</v>
+        <v>32.957701730076437</v>
       </c>
       <c r="D16" s="18">
         <f>B16/Einstellungen!B54</f>
-        <v>1.5851313920249033</v>
+        <v>1.6478850865038219</v>
       </c>
       <c r="E16" s="6">
         <f>B16/Einstellungen!B55</f>
-        <v>0.13209428266874193</v>
+        <v>0.13732375720865181</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -15834,19 +15835,19 @@
       </c>
       <c r="B17" s="18">
         <f>Spezifikation!J3+(1.28*Spezifikation!M3)</f>
-        <v>255.14824242003351</v>
+        <v>265.20019904931604</v>
       </c>
       <c r="C17" s="18">
         <f>B17/Einstellungen!B53</f>
-        <v>31.893530302504189</v>
+        <v>33.150024881164505</v>
       </c>
       <c r="D17" s="18">
         <f>B17/Einstellungen!B54</f>
-        <v>1.5946765151252094</v>
+        <v>1.6575012440582253</v>
       </c>
       <c r="E17" s="6">
         <f>B17/Einstellungen!B55</f>
-        <v>0.13288970959376745</v>
+        <v>0.13812510367151878</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -15855,19 +15856,19 @@
       </c>
       <c r="B18" s="26">
         <f>Spezifikation!J3+(2*Spezifikation!M3)</f>
-        <v>259.07537878130239</v>
+        <v>269.1565610145563</v>
       </c>
       <c r="C18" s="26">
         <f>B18/Einstellungen!B53</f>
-        <v>32.384422347662799</v>
+        <v>33.644570126819538</v>
       </c>
       <c r="D18" s="26">
         <f>B18/Einstellungen!B54</f>
-        <v>1.6192211173831399</v>
+        <v>1.682228506340977</v>
       </c>
       <c r="E18" s="136">
         <f>B18/Einstellungen!B55</f>
-        <v>0.13493509311526167</v>
+        <v>0.14018570886174808</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -16004,19 +16005,19 @@
       </c>
       <c r="C14" s="32">
         <f>Aufwandschätzung!B8</f>
-        <v>244.51224810826369</v>
+        <v>254.48505206012359</v>
       </c>
       <c r="D14" s="32">
         <f>Aufwandschätzung!B11</f>
-        <v>248.16666666666666</v>
+        <v>258.16666666666663</v>
       </c>
       <c r="E14" s="32">
         <f>Aufwandschätzung!B14</f>
-        <v>251.82108522506962</v>
+        <v>261.84828127320969</v>
       </c>
       <c r="F14" s="33">
         <f>Aufwandschätzung!B18</f>
-        <v>259.07537878130239</v>
+        <v>269.1565610145563</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -16025,19 +16026,19 @@
       </c>
       <c r="C15" s="34">
         <f>C14/C6</f>
-        <v>31.754837416657622</v>
+        <v>33.050006761055009</v>
       </c>
       <c r="D15" s="34">
         <f>D14/C6</f>
-        <v>32.229437229437231</v>
+        <v>33.52813852813852</v>
       </c>
       <c r="E15" s="34">
         <f>E14/C6</f>
-        <v>32.704037042216832</v>
+        <v>34.006270295222038</v>
       </c>
       <c r="F15" s="35">
         <f>F14/C6</f>
-        <v>33.64615308848083</v>
+        <v>34.955397534357964</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -16087,19 +16088,19 @@
       </c>
       <c r="C19" s="38">
         <f>(C5*C14)+C16+C17</f>
-        <v>33987.202487048657</v>
+        <v>35373.422236357183</v>
       </c>
       <c r="D19" s="38">
         <f>(C5*D14)+D16+D17</f>
-        <v>34495.166666666664</v>
+        <v>35885.166666666664</v>
       </c>
       <c r="E19" s="38">
         <f>(C5*E14)+E16+E17</f>
-        <v>35003.130846284679</v>
+        <v>36396.911096976146</v>
       </c>
       <c r="F19" s="40">
         <f>(C5*F14)+F16+F17</f>
-        <v>36011.477650601031</v>
+        <v>37412.761981023323</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">

--- a/DAGoPERT_AILV.xlsx
+++ b/DAGoPERT_AILV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elena\Desktop\FH\INNO\AILV-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75581E5C-1CF3-4858-84EF-48E6C2E81B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47547DA1-7711-4EAB-8972-5D0006D10A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="636" yWindow="3360" windowWidth="22404" windowHeight="8880" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="22404" windowHeight="8880" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="18" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="173">
   <si>
     <t>Umsetzung</t>
   </si>
@@ -613,6 +613,9 @@
   </si>
   <si>
     <t>10.3</t>
+  </si>
+  <si>
+    <t>Export Archive</t>
   </si>
 </sst>
 </file>
@@ -1840,49 +1843,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.5448548269923559</c:v>
+                  <c:v>1.535572289403349</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5695820892751076</c:v>
+                  <c:v>1.5597037652181434</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5791982468295112</c:v>
+                  <c:v>1.5690882280350078</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5846931940034561</c:v>
+                  <c:v>1.574450778216073</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5905315753757725</c:v>
+                  <c:v>1.5801484877834551</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5956830883513455</c:v>
+                  <c:v>1.585175878578204</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6049558117073777</c:v>
+                  <c:v>1.5942251820087516</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6135416666666664</c:v>
+                  <c:v>1.6026041666666664</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.6221275216259552</c:v>
+                  <c:v>1.6109831513245811</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.6314002449819871</c:v>
+                  <c:v>1.620032454755129</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.6365517579575606</c:v>
+                  <c:v>1.6250598455498779</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.642390139329877</c:v>
+                  <c:v>1.6307575551172597</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.6478850865038219</c:v>
+                  <c:v>1.6361201052983252</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.6575012440582253</c:v>
+                  <c:v>1.6455045681151894</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.682228506340977</c:v>
+                  <c:v>1.6696360439299838</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3181,7 +3184,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Tabelle3"/>
-  <dimension ref="A1:Q363"/>
+  <dimension ref="A1:Q364"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="132" customWidth="1"/>
@@ -3286,35 +3289,35 @@
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
       <c r="E3" s="127">
-        <f>SUM(E4:E10006)</f>
-        <v>179</v>
+        <f>SUM(E4:E10007)</f>
+        <v>182</v>
       </c>
       <c r="F3" s="55">
-        <f>SUM(F4:F10006)</f>
+        <f>SUM(F4:F10007)</f>
         <v>256</v>
       </c>
       <c r="G3" s="55">
-        <f>SUM(G4:G10006)</f>
-        <v>346</v>
+        <f>SUM(G4:G10007)</f>
+        <v>346.5</v>
       </c>
       <c r="H3" s="56"/>
       <c r="I3" s="57">
-        <f>SUM(I4:I10006)</f>
-        <v>258.16666666666663</v>
+        <f>SUM(I4:I10007)</f>
+        <v>258.75</v>
       </c>
       <c r="J3" s="58">
-        <f>SUM(J4:J10006)</f>
-        <v>258.16666666666663</v>
+        <f>SUM(J4:J10007)</f>
+        <v>256.41666666666663</v>
       </c>
       <c r="K3" s="57"/>
       <c r="L3" s="57"/>
       <c r="M3" s="103">
         <f>N3^(1/2)</f>
-        <v>5.494947173944845</v>
+        <v>5.3625501810653891</v>
       </c>
       <c r="N3" s="121">
-        <f>SUM(N4:N10006)</f>
-        <v>30.194444444444439</v>
+        <f>SUM(N4:N10007)</f>
+        <v>28.756944444444439</v>
       </c>
       <c r="O3" s="114"/>
       <c r="P3" s="59"/>
@@ -3348,26 +3351,26 @@
         <v>5.166666666666667</v>
       </c>
       <c r="J4" s="141">
-        <f t="shared" ref="J4:J71" si="0">IF(I4="","",I4*storypoints_kalibrierung)</f>
+        <f t="shared" ref="J4:J72" si="0">IF(I4="","",I4*storypoints_kalibrierung)</f>
         <v>5.166666666666667</v>
       </c>
       <c r="K4" s="142">
         <v>99.73</v>
       </c>
       <c r="L4" s="143">
-        <f t="shared" ref="L4:L55" si="1">INDEX(prozentsatz_divisor,(MATCH(K4,prozentsatz_divisor_prozent,-1)+1),2)</f>
+        <f t="shared" ref="L4:L56" si="1">INDEX(prozentsatz_divisor,(MATCH(K4,prozentsatz_divisor_prozent,-1)+1),2)</f>
         <v>6</v>
       </c>
       <c r="M4" s="144">
-        <f t="shared" ref="M4:M58" si="2">IF(I4="","",((G4-E4)/L4)*storypoints_kalibrierung)</f>
+        <f t="shared" ref="M4:M59" si="2">IF(I4="","",((G4-E4)/L4)*storypoints_kalibrierung)</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="N4" s="145">
-        <f t="shared" ref="N4:N71" si="3">IF(I4="","",M4^2)</f>
+        <f t="shared" ref="N4:N72" si="3">IF(I4="","",M4^2)</f>
         <v>0.69444444444444453</v>
       </c>
       <c r="O4" s="146" t="str">
-        <f t="shared" ref="O4:O36" si="4">IF(J4="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I4,storypoints_kalibrierung_aufsize,-1),3))</f>
+        <f t="shared" ref="O4:O37" si="4">IF(J4="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I4,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v>M</v>
       </c>
       <c r="P4" s="117"/>
@@ -3396,7 +3399,7 @@
       </c>
       <c r="H5" s="131"/>
       <c r="I5" s="140">
-        <f t="shared" ref="I5:I33" si="5">IF(OR(E5="",F5="",G5=""),"",(E5+(4*F5)+G5)/6)</f>
+        <f t="shared" ref="I5:I34" si="5">IF(OR(E5="",F5="",G5=""),"",(E5+(4*F5)+G5)/6)</f>
         <v>6.166666666666667</v>
       </c>
       <c r="J5" s="141">
@@ -3525,7 +3528,7 @@
       </c>
       <c r="P7" s="117"/>
       <c r="Q7" s="118" t="str">
-        <f t="shared" ref="Q7:Q37" si="7">IF(OR(O7="",P7=""),"",INDEX(businessvalue_kalibrierung, MATCH(O7,businessvalue_kalibrierung_aufwand,0),MATCH(P7,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" ref="Q7:Q38" si="7">IF(OR(O7="",P7=""),"",INDEX(businessvalue_kalibrierung, MATCH(O7,businessvalue_kalibrierung_aufwand,0),MATCH(P7,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
@@ -4166,22 +4169,22 @@
         <v>111</v>
       </c>
       <c r="E20" s="139">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F20" s="139">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G20" s="139">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H20" s="131"/>
       <c r="I20" s="140">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="J20" s="141">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="K20" s="142">
         <v>99.73</v>
@@ -4544,22 +4547,22 @@
         <v>107</v>
       </c>
       <c r="E27" s="139">
+        <v>11</v>
+      </c>
+      <c r="F27" s="139">
         <v>12</v>
       </c>
-      <c r="F27" s="139">
-        <v>16</v>
-      </c>
       <c r="G27" s="139">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H27" s="131"/>
       <c r="I27" s="140">
         <f t="shared" si="5"/>
-        <v>15.833333333333334</v>
+        <v>12</v>
       </c>
       <c r="J27" s="141">
         <f t="shared" si="0"/>
-        <v>15.833333333333334</v>
+        <v>12</v>
       </c>
       <c r="K27" s="142">
         <v>99.73</v>
@@ -4570,11 +4573,11 @@
       </c>
       <c r="M27" s="144">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N27" s="145">
         <f t="shared" si="3"/>
-        <v>1.3611111111111114</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="O27" s="146" t="str">
         <f t="shared" si="4"/>
@@ -4586,68 +4589,46 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="150" t="s">
-        <v>159</v>
-      </c>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="150"/>
       <c r="B28" s="131"/>
-      <c r="C28" s="148" t="s">
-        <v>97</v>
-      </c>
+      <c r="C28" s="131"/>
       <c r="D28" s="131" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="E28" s="139">
+        <v>1</v>
+      </c>
+      <c r="F28" s="139">
+        <v>2</v>
+      </c>
+      <c r="G28" s="139">
         <v>5</v>
-      </c>
-      <c r="F28" s="139">
-        <v>7</v>
-      </c>
-      <c r="G28" s="139">
-        <v>9</v>
       </c>
       <c r="H28" s="131"/>
       <c r="I28" s="140">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="J28" s="141">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="K28" s="142">
-        <v>99.73</v>
-      </c>
-      <c r="L28" s="143">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M28" s="144">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N28" s="145">
-        <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="O28" s="146" t="str">
-        <f t="shared" si="4"/>
-        <v>M</v>
-      </c>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="J28" s="141"/>
+      <c r="K28" s="142"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="144"/>
+      <c r="N28" s="145"/>
+      <c r="O28" s="146"/>
       <c r="P28" s="117"/>
-      <c r="Q28" s="118" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q28" s="118"/>
+    </row>
+    <row r="29" spans="1:17" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A29" s="150" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B29" s="131"/>
-      <c r="C29" s="131"/>
+      <c r="C29" s="148" t="s">
+        <v>97</v>
+      </c>
       <c r="D29" s="131" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E29" s="139">
         <v>5</v>
@@ -4694,30 +4675,30 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="150" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B30" s="131"/>
       <c r="C30" s="131"/>
       <c r="D30" s="131" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E30" s="139">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="139">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G30" s="139">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H30" s="131"/>
       <c r="I30" s="140">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J30" s="141">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K30" s="142">
         <v>99.73</v>
@@ -4744,36 +4725,32 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="150" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="131" t="s">
-        <v>100</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B31" s="131"/>
+      <c r="C31" s="131"/>
       <c r="D31" s="131" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E31" s="139">
         <v>3</v>
       </c>
       <c r="F31" s="139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="139">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" s="131"/>
       <c r="I31" s="140">
         <f t="shared" si="5"/>
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="J31" s="141">
         <f t="shared" si="0"/>
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K31" s="142">
         <v>99.73</v>
@@ -4784,11 +4761,11 @@
       </c>
       <c r="M31" s="144">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N31" s="145">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="O31" s="146" t="str">
         <f t="shared" si="4"/>
@@ -4800,32 +4777,36 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A32" s="150" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" s="147"/>
-      <c r="C32" s="131"/>
+        <v>153</v>
+      </c>
+      <c r="B32" s="147" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="131" t="s">
+        <v>100</v>
+      </c>
       <c r="D32" s="131" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E32" s="139">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F32" s="139">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G32" s="139">
-        <v>30</v>
+        <v>2.5</v>
       </c>
       <c r="H32" s="131"/>
       <c r="I32" s="140">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>1.9166666666666667</v>
       </c>
       <c r="J32" s="141">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>1.9166666666666667</v>
       </c>
       <c r="K32" s="142">
         <v>99.73</v>
@@ -4836,47 +4817,48 @@
       </c>
       <c r="M32" s="144">
         <f t="shared" si="2"/>
-        <v>2.3333333333333335</v>
+        <v>0.25</v>
       </c>
       <c r="N32" s="145">
         <f t="shared" si="3"/>
-        <v>5.4444444444444455</v>
+        <v>6.25E-2</v>
       </c>
       <c r="O32" s="146" t="str">
         <f t="shared" si="4"/>
-        <v>L</v>
+        <v>S</v>
       </c>
       <c r="P32" s="117"/>
-      <c r="Q32" s="118"/>
+      <c r="Q32" s="118" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="150" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B33" s="147"/>
-      <c r="C33" s="131" t="s">
-        <v>98</v>
-      </c>
+      <c r="C33" s="131"/>
       <c r="D33" s="131" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="E33" s="139">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F33" s="139">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G33" s="139">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H33" s="131"/>
       <c r="I33" s="140">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J33" s="141">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K33" s="142">
         <v>99.73</v>
@@ -4887,11 +4869,11 @@
       </c>
       <c r="M33" s="144">
         <f t="shared" si="2"/>
-        <v>1.6666666666666667</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="N33" s="145">
         <f t="shared" si="3"/>
-        <v>2.7777777777777781</v>
+        <v>5.4444444444444455</v>
       </c>
       <c r="O33" s="146" t="str">
         <f t="shared" si="4"/>
@@ -4902,30 +4884,32 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="150" t="s">
-        <v>169</v>
-      </c>
-      <c r="B34" s="131"/>
-      <c r="C34" s="131"/>
-      <c r="D34" s="147" t="s">
-        <v>128</v>
+        <v>163</v>
+      </c>
+      <c r="B34" s="147"/>
+      <c r="C34" s="131" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="131" t="s">
+        <v>127</v>
       </c>
       <c r="E34" s="139">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F34" s="139">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G34" s="139">
         <v>15</v>
       </c>
       <c r="H34" s="131"/>
       <c r="I34" s="140">
-        <f t="shared" ref="I34:I65" si="8">IF(OR(E34="",F34="",G34=""),"",(E34+(4*F34)+G34)/6)</f>
-        <v>11.833333333333334</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="J34" s="141">
         <f t="shared" si="0"/>
-        <v>11.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K34" s="142">
         <v>99.73</v>
@@ -4936,48 +4920,45 @@
       </c>
       <c r="M34" s="144">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="N34" s="145">
         <f t="shared" si="3"/>
-        <v>1.3611111111111114</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="O34" s="146" t="str">
         <f t="shared" si="4"/>
         <v>L</v>
       </c>
       <c r="P34" s="117"/>
-      <c r="Q34" s="118" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+      <c r="Q34" s="118"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="150" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B35" s="131"/>
       <c r="C35" s="131"/>
-      <c r="D35" s="131" t="s">
-        <v>160</v>
+      <c r="D35" s="147" t="s">
+        <v>128</v>
       </c>
       <c r="E35" s="139">
+        <v>8</v>
+      </c>
+      <c r="F35" s="139">
+        <v>12</v>
+      </c>
+      <c r="G35" s="139">
         <v>15</v>
-      </c>
-      <c r="F35" s="139">
-        <v>18</v>
-      </c>
-      <c r="G35" s="139">
-        <v>20</v>
       </c>
       <c r="H35" s="131"/>
       <c r="I35" s="140">
-        <f t="shared" si="8"/>
-        <v>17.833333333333332</v>
+        <f t="shared" ref="I35:I66" si="8">IF(OR(E35="",F35="",G35=""),"",(E35+(4*F35)+G35)/6)</f>
+        <v>11.833333333333334</v>
       </c>
       <c r="J35" s="141">
         <f t="shared" si="0"/>
-        <v>17.833333333333332</v>
+        <v>11.833333333333334</v>
       </c>
       <c r="K35" s="142">
         <v>99.73</v>
@@ -4988,11 +4969,11 @@
       </c>
       <c r="M35" s="144">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="N35" s="145">
         <f t="shared" si="3"/>
-        <v>0.69444444444444453</v>
+        <v>1.3611111111111114</v>
       </c>
       <c r="O35" s="146" t="str">
         <f t="shared" si="4"/>
@@ -5006,29 +4987,30 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="150" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B36" s="131"/>
-      <c r="D36" s="51" t="s">
-        <v>161</v>
+      <c r="C36" s="131"/>
+      <c r="D36" s="131" t="s">
+        <v>160</v>
       </c>
       <c r="E36" s="139">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F36" s="139">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G36" s="139">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H36" s="131"/>
       <c r="I36" s="140">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>17.833333333333332</v>
       </c>
       <c r="J36" s="141">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>17.833333333333332</v>
       </c>
       <c r="K36" s="142">
         <v>99.73</v>
@@ -5039,15 +5021,15 @@
       </c>
       <c r="M36" s="144">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="N36" s="145">
         <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
+        <v>0.69444444444444453</v>
       </c>
       <c r="O36" s="146" t="str">
         <f t="shared" si="4"/>
-        <v>M</v>
+        <v>L</v>
       </c>
       <c r="P36" s="117"/>
       <c r="Q36" s="118" t="str">
@@ -5056,19 +5038,30 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="150"/>
+      <c r="A37" s="150" t="s">
+        <v>171</v>
+      </c>
       <c r="B37" s="131"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
+      <c r="D37" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" s="139">
+        <v>2</v>
+      </c>
+      <c r="F37" s="139">
+        <v>4</v>
+      </c>
+      <c r="G37" s="139">
+        <v>6</v>
+      </c>
       <c r="H37" s="131"/>
-      <c r="I37" s="140" t="str">
+      <c r="I37" s="140">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J37" s="141" t="str">
+        <v>4</v>
+      </c>
+      <c r="J37" s="141">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K37" s="142">
         <v>99.73</v>
@@ -5077,17 +5070,17 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M37" s="144" t="str">
+      <c r="M37" s="144">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N37" s="145" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N37" s="145">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0.44444444444444442</v>
       </c>
       <c r="O37" s="146" t="str">
-        <f t="shared" ref="O37:O68" si="9">IF(J37="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I37,storypoints_kalibrierung_aufsize,-1),3))</f>
-        <v/>
+        <f t="shared" si="4"/>
+        <v>M</v>
       </c>
       <c r="P37" s="117"/>
       <c r="Q37" s="118" t="str">
@@ -5097,7 +5090,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="150"/>
-      <c r="B38" s="51"/>
+      <c r="B38" s="131"/>
       <c r="E38" s="51"/>
       <c r="F38" s="51"/>
       <c r="G38" s="51"/>
@@ -5126,12 +5119,12 @@
         <v/>
       </c>
       <c r="O38" s="146" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="O38:O69" si="9">IF(J38="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I38,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P38" s="117"/>
       <c r="Q38" s="118" t="str">
-        <f t="shared" ref="Q38" si="10">IF(OR(O38="",P38=""),"",INDEX(businessvalue_kalibrierung, MATCH(O38,businessvalue_kalibrierung_aufwand,0),MATCH(P38,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5171,13 +5164,13 @@
       </c>
       <c r="P39" s="117"/>
       <c r="Q39" s="118" t="str">
-        <f t="shared" ref="Q39:Q51" si="11">IF(OR(O39="",P39=""),"",INDEX(businessvalue_kalibrierung, MATCH(O39,businessvalue_kalibrierung_aufwand,0),MATCH(P39,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" ref="Q39" si="10">IF(OR(O39="",P39=""),"",INDEX(businessvalue_kalibrierung, MATCH(O39,businessvalue_kalibrierung_aufwand,0),MATCH(P39,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="150"/>
-      <c r="B40" s="131"/>
+      <c r="B40" s="51"/>
       <c r="E40" s="51"/>
       <c r="F40" s="51"/>
       <c r="G40" s="51"/>
@@ -5211,12 +5204,17 @@
       </c>
       <c r="P40" s="117"/>
       <c r="Q40" s="118" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="Q40:Q52" si="11">IF(OR(O40="",P40=""),"",INDEX(businessvalue_kalibrierung, MATCH(O40,businessvalue_kalibrierung_aufwand,0),MATCH(P40,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="150"/>
+      <c r="B41" s="131"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="131"/>
       <c r="I41" s="140" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5252,10 +5250,6 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="150"/>
-      <c r="D42" s="131"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
       <c r="I42" s="140" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5289,9 +5283,9 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="150"/>
-      <c r="C43" s="138"/>
+      <c r="D43" s="131"/>
       <c r="E43" s="139"/>
       <c r="F43" s="139"/>
       <c r="G43" s="139"/>
@@ -5328,9 +5322,9 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A44" s="150"/>
-      <c r="B44" s="130"/>
+      <c r="C44" s="138"/>
       <c r="E44" s="139"/>
       <c r="F44" s="139"/>
       <c r="G44" s="139"/>
@@ -5526,7 +5520,6 @@
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="150"/>
       <c r="B49" s="130"/>
-      <c r="C49" s="131"/>
       <c r="E49" s="139"/>
       <c r="F49" s="139"/>
       <c r="G49" s="139"/>
@@ -5566,6 +5559,7 @@
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="150"/>
       <c r="B50" s="130"/>
+      <c r="C50" s="131"/>
       <c r="E50" s="139"/>
       <c r="F50" s="139"/>
       <c r="G50" s="139"/>
@@ -5643,6 +5637,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="150"/>
+      <c r="B52" s="130"/>
       <c r="E52" s="139"/>
       <c r="F52" s="139"/>
       <c r="G52" s="139"/>
@@ -5675,13 +5670,12 @@
       </c>
       <c r="P52" s="117"/>
       <c r="Q52" s="118" t="str">
-        <f t="shared" ref="Q52:Q115" si="12">IF(OR(O52="",P52=""),"",INDEX(businessvalue_kalibrierung, MATCH(O52,businessvalue_kalibrierung_aufwand,0),MATCH(P52,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="150"/>
-      <c r="B53" s="130"/>
       <c r="E53" s="139"/>
       <c r="F53" s="139"/>
       <c r="G53" s="139"/>
@@ -5714,7 +5708,7 @@
       </c>
       <c r="P53" s="117"/>
       <c r="Q53" s="118" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="Q53:Q116" si="12">IF(OR(O53="",P53=""),"",INDEX(businessvalue_kalibrierung, MATCH(O53,businessvalue_kalibrierung_aufwand,0),MATCH(P53,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
@@ -5798,6 +5792,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="150"/>
+      <c r="B56" s="130"/>
       <c r="E56" s="139"/>
       <c r="F56" s="139"/>
       <c r="G56" s="139"/>
@@ -5812,8 +5807,8 @@
       <c r="K56" s="142">
         <v>99.73</v>
       </c>
-      <c r="L56" s="61">
-        <f t="shared" ref="L56:L115" si="13">INDEX(prozentsatz_divisor,(MATCH(K56,prozentsatz_divisor_prozent,-1)+1),2)</f>
+      <c r="L56" s="143">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="M56" s="144" t="str">
@@ -5836,7 +5831,6 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="150"/>
-      <c r="B57" s="130"/>
       <c r="E57" s="139"/>
       <c r="F57" s="139"/>
       <c r="G57" s="139"/>
@@ -5852,7 +5846,7 @@
         <v>99.73</v>
       </c>
       <c r="L57" s="61">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="L57:L116" si="13">INDEX(prozentsatz_divisor,(MATCH(K57,prozentsatz_divisor_prozent,-1)+1),2)</f>
         <v>6</v>
       </c>
       <c r="M57" s="144" t="str">
@@ -5914,6 +5908,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="150"/>
+      <c r="B59" s="130"/>
       <c r="E59" s="139"/>
       <c r="F59" s="139"/>
       <c r="G59" s="139"/>
@@ -5933,7 +5928,7 @@
         <v>6</v>
       </c>
       <c r="M59" s="144" t="str">
-        <f t="shared" ref="M59:M68" si="14">IF(I59="","",((G59-E59)/L59)*storypoints_kalibrierung)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N59" s="145" t="str">
@@ -5971,7 +5966,7 @@
         <v>6</v>
       </c>
       <c r="M60" s="144" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="M60:M69" si="14">IF(I60="","",((G60-E60)/L60)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N60" s="145" t="str">
@@ -5990,12 +5985,9 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="150"/>
-      <c r="C61" s="123"/>
-      <c r="D61" s="123"/>
       <c r="E61" s="139"/>
       <c r="F61" s="139"/>
       <c r="G61" s="139"/>
-      <c r="H61" s="124"/>
       <c r="I61" s="140" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -6202,7 +6194,7 @@
       <c r="G66" s="139"/>
       <c r="H66" s="124"/>
       <c r="I66" s="140" t="str">
-        <f t="shared" ref="I66:I71" si="15">IF(OR(E66="",F66="",G66=""),"",(E66+(4*F66)+G66)/6)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J66" s="141" t="str">
@@ -6243,7 +6235,7 @@
       <c r="G67" s="139"/>
       <c r="H67" s="124"/>
       <c r="I67" s="140" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="I67:I72" si="15">IF(OR(E67="",F67="",G67=""),"",(E67+(4*F67)+G67)/6)</f>
         <v/>
       </c>
       <c r="J67" s="141" t="str">
@@ -6317,6 +6309,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="150"/>
       <c r="C69" s="123"/>
       <c r="D69" s="123"/>
       <c r="E69" s="139"/>
@@ -6339,7 +6332,7 @@
         <v>6</v>
       </c>
       <c r="M69" s="144" t="str">
-        <f t="shared" ref="M69:M100" si="16">IF(I69="","",((G69-E69)/L69)*storypoints_kalibrierung)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N69" s="145" t="str">
@@ -6347,7 +6340,7 @@
         <v/>
       </c>
       <c r="O69" s="146" t="str">
-        <f t="shared" ref="O69:O100" si="17">IF(J69="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I69,storypoints_kalibrierung_aufsize,-1),3))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P69" s="117"/>
@@ -6379,7 +6372,7 @@
         <v>6</v>
       </c>
       <c r="M70" s="144" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="M70:M101" si="16">IF(I70="","",((G70-E70)/L70)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N70" s="145" t="str">
@@ -6387,7 +6380,7 @@
         <v/>
       </c>
       <c r="O70" s="146" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="O70:O101" si="17">IF(J70="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I70,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P70" s="117"/>
@@ -6444,11 +6437,11 @@
       <c r="G72" s="139"/>
       <c r="H72" s="124"/>
       <c r="I72" s="140" t="str">
-        <f t="shared" ref="I72:I79" si="18">IF(OR(E72="",F72="",G72=""),"",(E72+(4*F72)+G72)/6)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J72" s="141" t="str">
-        <f t="shared" ref="J72:J75" si="19">IF(I72="","",I72*storypoints_kalibrierung)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K72" s="142">
@@ -6463,7 +6456,7 @@
         <v/>
       </c>
       <c r="N72" s="145" t="str">
-        <f t="shared" ref="N72:N74" si="20">IF(I72="","",M72^2)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O72" s="146" t="str">
@@ -6484,11 +6477,11 @@
       <c r="G73" s="139"/>
       <c r="H73" s="124"/>
       <c r="I73" s="140" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="I73:I80" si="18">IF(OR(E73="",F73="",G73=""),"",(E73+(4*F73)+G73)/6)</f>
         <v/>
       </c>
       <c r="J73" s="141" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="J73:J76" si="19">IF(I73="","",I73*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="K73" s="142">
@@ -6503,7 +6496,7 @@
         <v/>
       </c>
       <c r="N73" s="145" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="N73:N75" si="20">IF(I73="","",M73^2)</f>
         <v/>
       </c>
       <c r="O73" s="146" t="str">
@@ -6583,7 +6576,7 @@
         <v/>
       </c>
       <c r="N75" s="145" t="str">
-        <f t="shared" ref="N75:N135" si="21">IF(I75="","",M75^2)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O75" s="146" t="str">
@@ -6608,7 +6601,7 @@
         <v/>
       </c>
       <c r="J76" s="141" t="str">
-        <f t="shared" ref="J76:J135" si="22">IF(I76="","",I76*storypoints_kalibrierung)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K76" s="142">
@@ -6623,7 +6616,7 @@
         <v/>
       </c>
       <c r="N76" s="145" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="N76:N136" si="21">IF(I76="","",M76^2)</f>
         <v/>
       </c>
       <c r="O76" s="146" t="str">
@@ -6648,7 +6641,7 @@
         <v/>
       </c>
       <c r="J77" s="141" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="J77:J136" si="22">IF(I77="","",I77*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="K77" s="142">
@@ -6691,7 +6684,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K78" s="52">
+      <c r="K78" s="142">
         <v>99.73</v>
       </c>
       <c r="L78" s="61">
@@ -6763,8 +6756,8 @@
       <c r="F80" s="139"/>
       <c r="G80" s="139"/>
       <c r="H80" s="124"/>
-      <c r="I80" s="62" t="str">
-        <f t="shared" ref="I80:I137" si="23">IF(OR(E80="",F80="",G80=""),"",(E80+(4*F80)+G80)/6)</f>
+      <c r="I80" s="140" t="str">
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J80" s="141" t="str">
@@ -6804,7 +6797,7 @@
       <c r="G81" s="139"/>
       <c r="H81" s="124"/>
       <c r="I81" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="I81:I138" si="23">IF(OR(E81="",F81="",G81=""),"",(E81+(4*F81)+G81)/6)</f>
         <v/>
       </c>
       <c r="J81" s="141" t="str">
@@ -7619,7 +7612,7 @@
         <v>6</v>
       </c>
       <c r="M101" s="144" t="str">
-        <f t="shared" ref="M101:M132" si="24">IF(I101="","",((G101-E101)/L101)*storypoints_kalibrierung)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="N101" s="145" t="str">
@@ -7627,7 +7620,7 @@
         <v/>
       </c>
       <c r="O101" s="146" t="str">
-        <f t="shared" ref="O101:O132" si="25">IF(J101="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I101,storypoints_kalibrierung_aufsize,-1),3))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P101" s="117"/>
@@ -7659,7 +7652,7 @@
         <v>6</v>
       </c>
       <c r="M102" s="144" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="M102:M133" si="24">IF(I102="","",((G102-E102)/L102)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N102" s="145" t="str">
@@ -7667,7 +7660,7 @@
         <v/>
       </c>
       <c r="O102" s="146" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="O102:O133" si="25">IF(J102="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I102,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P102" s="117"/>
@@ -7757,9 +7750,12 @@
       </c>
     </row>
     <row r="105" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C105" s="123"/>
+      <c r="D105" s="123"/>
       <c r="E105" s="139"/>
       <c r="F105" s="139"/>
       <c r="G105" s="139"/>
+      <c r="H105" s="124"/>
       <c r="I105" s="62" t="str">
         <f t="shared" si="23"/>
         <v/>
@@ -8179,7 +8175,7 @@
         <v>99.73</v>
       </c>
       <c r="L116" s="61">
-        <f t="shared" ref="L116:L179" si="26">INDEX(prozentsatz_divisor,(MATCH(K116,prozentsatz_divisor_prozent,-1)+1),2)</f>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="M116" s="144" t="str">
@@ -8196,7 +8192,7 @@
       </c>
       <c r="P116" s="117"/>
       <c r="Q116" s="118" t="str">
-        <f t="shared" ref="Q116:Q179" si="27">IF(OR(O116="",P116=""),"",INDEX(businessvalue_kalibrierung, MATCH(O116,businessvalue_kalibrierung_aufwand,0),MATCH(P116,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -8216,7 +8212,7 @@
         <v>99.73</v>
       </c>
       <c r="L117" s="61">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="L117:L180" si="26">INDEX(prozentsatz_divisor,(MATCH(K117,prozentsatz_divisor_prozent,-1)+1),2)</f>
         <v>6</v>
       </c>
       <c r="M117" s="144" t="str">
@@ -8233,7 +8229,7 @@
       </c>
       <c r="P117" s="117"/>
       <c r="Q117" s="118" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="Q117:Q180" si="27">IF(OR(O117="",P117=""),"",INDEX(businessvalue_kalibrierung, MATCH(O117,businessvalue_kalibrierung_aufwand,0),MATCH(P117,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
@@ -8423,6 +8419,9 @@
       </c>
     </row>
     <row r="123" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E123" s="139"/>
+      <c r="F123" s="139"/>
+      <c r="G123" s="139"/>
       <c r="I123" s="62" t="str">
         <f t="shared" si="23"/>
         <v/>
@@ -8779,7 +8778,7 @@
         <v>6</v>
       </c>
       <c r="M133" s="144" t="str">
-        <f t="shared" ref="M133:M143" si="28">IF(I133="","",((G133-E133)/L133)*storypoints_kalibrierung)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N133" s="145" t="str">
@@ -8787,7 +8786,7 @@
         <v/>
       </c>
       <c r="O133" s="146" t="str">
-        <f t="shared" ref="O133:O164" si="29">IF(J133="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I133,storypoints_kalibrierung_aufsize,-1),3))</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="P133" s="117"/>
@@ -8813,7 +8812,7 @@
         <v>6</v>
       </c>
       <c r="M134" s="144" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="M134:M144" si="28">IF(I134="","",((G134-E134)/L134)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N134" s="145" t="str">
@@ -8821,7 +8820,7 @@
         <v/>
       </c>
       <c r="O134" s="146" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="O134:O165" si="29">IF(J134="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I134,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P134" s="117"/>
@@ -8869,8 +8868,8 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J136" s="63" t="str">
-        <f t="shared" ref="J136:J137" si="30">IF(I136="","",I136*storypoints_kalibrierung)</f>
+      <c r="J136" s="141" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K136" s="52">
@@ -8885,7 +8884,7 @@
         <v/>
       </c>
       <c r="N136" s="145" t="str">
-        <f t="shared" ref="N136:N149" si="31">IF(I136="","",M136^2)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="O136" s="146" t="str">
@@ -8904,7 +8903,7 @@
         <v/>
       </c>
       <c r="J137" s="63" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="J137:J138" si="30">IF(I137="","",I137*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="K137" s="52">
@@ -8919,7 +8918,7 @@
         <v/>
       </c>
       <c r="N137" s="145" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="N137:N150" si="31">IF(I137="","",M137^2)</f>
         <v/>
       </c>
       <c r="O137" s="146" t="str">
@@ -8934,11 +8933,11 @@
     </row>
     <row r="138" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I138" s="62" t="str">
-        <f t="shared" ref="I138:I201" si="32">IF(OR(E138="",F138="",G138=""),"",(E138+(4*F138)+G138)/6)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J138" s="63" t="str">
-        <f t="shared" ref="J138:J201" si="33">IF(I138="","",I138*storypoints_kalibrierung)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K138" s="52">
@@ -8968,11 +8967,11 @@
     </row>
     <row r="139" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I139" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="I139:I202" si="32">IF(OR(E139="",F139="",G139=""),"",(E139+(4*F139)+G139)/6)</f>
         <v/>
       </c>
       <c r="J139" s="63" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="J139:J202" si="33">IF(I139="","",I139*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="K139" s="52">
@@ -9152,8 +9151,8 @@
         <f t="shared" si="26"/>
         <v>6</v>
       </c>
-      <c r="M144" s="64" t="str">
-        <f t="shared" ref="M144:M201" si="34">IF(I144="","",((G144-E144)/L144)*storypoints_kalibrierung)</f>
+      <c r="M144" s="144" t="str">
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="N144" s="145" t="str">
@@ -9187,7 +9186,7 @@
         <v>6</v>
       </c>
       <c r="M145" s="64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="M145:M202" si="34">IF(I145="","",((G145-E145)/L145)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N145" s="145" t="str">
@@ -9360,8 +9359,8 @@
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="N150" s="122" t="str">
-        <f t="shared" ref="N150:N201" si="35">IF(I150="","",M150^2)</f>
+      <c r="N150" s="145" t="str">
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="O150" s="146" t="str">
@@ -9395,7 +9394,7 @@
         <v/>
       </c>
       <c r="N151" s="122" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="N151:N202" si="35">IF(I151="","",M151^2)</f>
         <v/>
       </c>
       <c r="O151" s="146" t="str">
@@ -9875,7 +9874,7 @@
         <v/>
       </c>
       <c r="O165" s="146" t="str">
-        <f t="shared" ref="O165:O172" si="36">IF(J165="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I165,storypoints_kalibrierung_aufsize,-1),3))</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P165" s="117"/>
@@ -9909,7 +9908,7 @@
         <v/>
       </c>
       <c r="O166" s="146" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="O166:O173" si="36">IF(J166="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I166,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P166" s="117"/>
@@ -10146,8 +10145,8 @@
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="O173" s="116" t="str">
-        <f t="shared" ref="O173:O199" si="37">IF(J173="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I173,storypoints_kalibrierung_aufsize,-1),3))</f>
+      <c r="O173" s="146" t="str">
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="P173" s="117"/>
@@ -10181,7 +10180,7 @@
         <v/>
       </c>
       <c r="O174" s="116" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="O174:O200" si="37">IF(J174="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I174,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P174" s="117"/>
@@ -10373,7 +10372,7 @@
         <v>99.73</v>
       </c>
       <c r="L180" s="61">
-        <f t="shared" ref="L180:L243" si="38">INDEX(prozentsatz_divisor,(MATCH(K180,prozentsatz_divisor_prozent,-1)+1),2)</f>
+        <f t="shared" si="26"/>
         <v>6</v>
       </c>
       <c r="M180" s="64" t="str">
@@ -10390,7 +10389,7 @@
       </c>
       <c r="P180" s="117"/>
       <c r="Q180" s="118" t="str">
-        <f t="shared" ref="Q180:Q243" si="39">IF(OR(O180="",P180=""),"",INDEX(businessvalue_kalibrierung, MATCH(O180,businessvalue_kalibrierung_aufwand,0),MATCH(P180,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
@@ -10407,7 +10406,7 @@
         <v>99.73</v>
       </c>
       <c r="L181" s="61">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="L181:L244" si="38">INDEX(prozentsatz_divisor,(MATCH(K181,prozentsatz_divisor_prozent,-1)+1),2)</f>
         <v>6</v>
       </c>
       <c r="M181" s="64" t="str">
@@ -10424,7 +10423,7 @@
       </c>
       <c r="P181" s="117"/>
       <c r="Q181" s="118" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="Q181:Q244" si="39">IF(OR(O181="",P181=""),"",INDEX(businessvalue_kalibrierung, MATCH(O181,businessvalue_kalibrierung_aufwand,0),MATCH(P181,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
@@ -11065,7 +11064,7 @@
         <v/>
       </c>
       <c r="O200" s="116" t="str">
-        <f t="shared" ref="O200:O263" si="40">IF(J200="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I200,storypoints_kalibrierung_aufsize,-1),3))</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P200" s="117"/>
@@ -11099,7 +11098,7 @@
         <v/>
       </c>
       <c r="O201" s="116" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="O201:O264" si="40">IF(J201="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I201,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P201" s="117"/>
@@ -11110,11 +11109,11 @@
     </row>
     <row r="202" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I202" s="62" t="str">
-        <f t="shared" ref="I202:I265" si="41">IF(OR(E202="",F202="",G202=""),"",(E202+(4*F202)+G202)/6)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J202" s="63" t="str">
-        <f t="shared" ref="J202:J265" si="42">IF(I202="","",I202*storypoints_kalibrierung)</f>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K202" s="52">
@@ -11125,11 +11124,11 @@
         <v>6</v>
       </c>
       <c r="M202" s="64" t="str">
-        <f t="shared" ref="M202:M265" si="43">IF(I202="","",((G202-E202)/L202)*storypoints_kalibrierung)</f>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N202" s="122" t="str">
-        <f t="shared" ref="N202:N265" si="44">IF(I202="","",M202^2)</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O202" s="116" t="str">
@@ -11144,11 +11143,11 @@
     </row>
     <row r="203" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I203" s="62" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="I203:I266" si="41">IF(OR(E203="",F203="",G203=""),"",(E203+(4*F203)+G203)/6)</f>
         <v/>
       </c>
       <c r="J203" s="63" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="J203:J266" si="42">IF(I203="","",I203*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="K203" s="52">
@@ -11159,11 +11158,11 @@
         <v>6</v>
       </c>
       <c r="M203" s="64" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="M203:M266" si="43">IF(I203="","",((G203-E203)/L203)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N203" s="122" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="N203:N266" si="44">IF(I203="","",M203^2)</f>
         <v/>
       </c>
       <c r="O203" s="116" t="str">
@@ -12549,7 +12548,7 @@
         <v>99.73</v>
       </c>
       <c r="L244" s="61">
-        <f t="shared" ref="L244:L307" si="45">INDEX(prozentsatz_divisor,(MATCH(K244,prozentsatz_divisor_prozent,-1)+1),2)</f>
+        <f t="shared" si="38"/>
         <v>6</v>
       </c>
       <c r="M244" s="64" t="str">
@@ -12566,7 +12565,7 @@
       </c>
       <c r="P244" s="117"/>
       <c r="Q244" s="118" t="str">
-        <f t="shared" ref="Q244:Q307" si="46">IF(OR(O244="",P244=""),"",INDEX(businessvalue_kalibrierung, MATCH(O244,businessvalue_kalibrierung_aufwand,0),MATCH(P244,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12583,7 +12582,7 @@
         <v>99.73</v>
       </c>
       <c r="L245" s="61">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="L245:L308" si="45">INDEX(prozentsatz_divisor,(MATCH(K245,prozentsatz_divisor_prozent,-1)+1),2)</f>
         <v>6</v>
       </c>
       <c r="M245" s="64" t="str">
@@ -12600,7 +12599,7 @@
       </c>
       <c r="P245" s="117"/>
       <c r="Q245" s="118" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="Q245:Q308" si="46">IF(OR(O245="",P245=""),"",INDEX(businessvalue_kalibrierung, MATCH(O245,businessvalue_kalibrierung_aufwand,0),MATCH(P245,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
@@ -13241,7 +13240,7 @@
         <v/>
       </c>
       <c r="O264" s="116" t="str">
-        <f t="shared" ref="O264:O322" si="47">IF(J264="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I264,storypoints_kalibrierung_aufsize,-1),3))</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="P264" s="117"/>
@@ -13275,7 +13274,7 @@
         <v/>
       </c>
       <c r="O265" s="116" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" ref="O265:O323" si="47">IF(J265="","",INDEX(storypoints_kalibrierung_shirtsizes, MATCH(I265,storypoints_kalibrierung_aufsize,-1),3))</f>
         <v/>
       </c>
       <c r="P265" s="117"/>
@@ -13286,11 +13285,11 @@
     </row>
     <row r="266" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I266" s="62" t="str">
-        <f t="shared" ref="I266:I322" si="48">IF(OR(E266="",F266="",G266=""),"",(E266+(4*F266)+G266)/6)</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="J266" s="63" t="str">
-        <f t="shared" ref="J266:J322" si="49">IF(I266="","",I266*storypoints_kalibrierung)</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="K266" s="52">
@@ -13301,11 +13300,11 @@
         <v>6</v>
       </c>
       <c r="M266" s="64" t="str">
-        <f t="shared" ref="M266:M322" si="50">IF(I266="","",((G266-E266)/L266)*storypoints_kalibrierung)</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N266" s="122" t="str">
-        <f t="shared" ref="N266:N322" si="51">IF(I266="","",M266^2)</f>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="O266" s="116" t="str">
@@ -13320,11 +13319,11 @@
     </row>
     <row r="267" spans="9:17" x14ac:dyDescent="0.25">
       <c r="I267" s="62" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="I267:I323" si="48">IF(OR(E267="",F267="",G267=""),"",(E267+(4*F267)+G267)/6)</f>
         <v/>
       </c>
       <c r="J267" s="63" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" ref="J267:J323" si="49">IF(I267="","",I267*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="K267" s="52">
@@ -13335,11 +13334,11 @@
         <v>6</v>
       </c>
       <c r="M267" s="64" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" ref="M267:M323" si="50">IF(I267="","",((G267-E267)/L267)*storypoints_kalibrierung)</f>
         <v/>
       </c>
       <c r="N267" s="122" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="N267:N323" si="51">IF(I267="","",M267^2)</f>
         <v/>
       </c>
       <c r="O267" s="116" t="str">
@@ -14725,7 +14724,7 @@
         <v>99.73</v>
       </c>
       <c r="L308" s="61">
-        <f t="shared" ref="L308:L322" si="52">INDEX(prozentsatz_divisor,(MATCH(K308,prozentsatz_divisor_prozent,-1)+1),2)</f>
+        <f t="shared" si="45"/>
         <v>6</v>
       </c>
       <c r="M308" s="64" t="str">
@@ -14742,7 +14741,7 @@
       </c>
       <c r="P308" s="117"/>
       <c r="Q308" s="118" t="str">
-        <f t="shared" ref="Q308:Q322" si="53">IF(OR(O308="",P308=""),"",INDEX(businessvalue_kalibrierung, MATCH(O308,businessvalue_kalibrierung_aufwand,0),MATCH(P308,businessvalue_kalibrierung_businesswert,0)))</f>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -14759,7 +14758,7 @@
         <v>99.73</v>
       </c>
       <c r="L309" s="61">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="L309:L323" si="52">INDEX(prozentsatz_divisor,(MATCH(K309,prozentsatz_divisor_prozent,-1)+1),2)</f>
         <v>6</v>
       </c>
       <c r="M309" s="64" t="str">
@@ -14776,7 +14775,7 @@
       </c>
       <c r="P309" s="117"/>
       <c r="Q309" s="118" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="Q309:Q323" si="53">IF(OR(O309="",P309=""),"",INDEX(businessvalue_kalibrierung, MATCH(O309,businessvalue_kalibrierung_aufwand,0),MATCH(P309,businessvalue_kalibrierung_businesswert,0)))</f>
         <v/>
       </c>
     </row>
@@ -15223,17 +15222,45 @@
       </c>
     </row>
     <row r="323" spans="9:17" x14ac:dyDescent="0.25">
+      <c r="I323" s="62" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="J323" s="63" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="K323" s="52">
+        <v>99.73</v>
+      </c>
+      <c r="L323" s="61">
+        <f t="shared" si="52"/>
+        <v>6</v>
+      </c>
       <c r="M323" s="64" t="str">
-        <f t="shared" ref="M323:M327" si="54">IF(I323="","",((G323-E323)/L323)*storypoints_kalibrierung)</f>
-        <v/>
-      </c>
-      <c r="N323" s="122"/>
+        <f t="shared" si="50"/>
+        <v/>
+      </c>
+      <c r="N323" s="122" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="O323" s="116" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="P323" s="117"/>
+      <c r="Q323" s="118" t="str">
+        <f t="shared" si="53"/>
+        <v/>
+      </c>
     </row>
     <row r="324" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M324" s="64" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
+        <f t="shared" ref="M324:M328" si="54">IF(I324="","",((G324-E324)/L324)*storypoints_kalibrierung)</f>
+        <v/>
+      </c>
+      <c r="N324" s="122"/>
     </row>
     <row r="325" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M325" s="64" t="str">
@@ -15255,13 +15282,13 @@
     </row>
     <row r="328" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M328" s="64" t="str">
-        <f t="shared" ref="M328:M363" si="55">IF(I328="","",((G328-E328)/L328)*storypoints_kalibrierung)</f>
+        <f t="shared" si="54"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="9:17" x14ac:dyDescent="0.25">
       <c r="M329" s="64" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="M329:M364" si="55">IF(I329="","",((G329-E329)/L329)*storypoints_kalibrierung)</f>
         <v/>
       </c>
     </row>
@@ -15465,6 +15492,12 @@
     </row>
     <row r="363" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M363" s="64" t="str">
+        <f t="shared" si="55"/>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M364" s="64" t="str">
         <f t="shared" si="55"/>
         <v/>
       </c>
@@ -15477,10 +15510,10 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P4:P322" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P4:P323" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>shirtsizes</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1379" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1380" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>5</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -15493,7 +15526,7 @@
     <oddFooter>&amp;L(c) 2006 DI(FH) Sven Schweiger&amp;R&amp;P / &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="548" max="16383" man="1"/>
+    <brk id="549" max="16383" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>
@@ -15562,19 +15595,19 @@
       </c>
       <c r="B4" s="23">
         <f>IF((Spezifikation!J3-(2*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(2*Spezifikation!M3)))</f>
-        <v>247.17677231877693</v>
+        <v>245.69156630453585</v>
       </c>
       <c r="C4" s="18">
         <f>IF(B4="NV",C5,B4/Einstellungen!$B$53)</f>
-        <v>30.897096539847116</v>
+        <v>30.711445788066982</v>
       </c>
       <c r="D4" s="18">
         <f>IF(B4="NV",D5,B4/Einstellungen!$B$54)</f>
-        <v>1.5448548269923559</v>
+        <v>1.535572289403349</v>
       </c>
       <c r="E4" s="6">
         <f>IF(B4="NV",E5,B4/Einstellungen!$B$55)</f>
-        <v>0.12873790224936299</v>
+        <v>0.12796435745027909</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -15583,19 +15616,19 @@
       </c>
       <c r="B5" s="23">
         <f>IF((Spezifikation!J3-(1.28*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1.28*Spezifikation!M3)))</f>
-        <v>251.13313428401722</v>
+        <v>249.55260243490292</v>
       </c>
       <c r="C5" s="18">
         <f>IF(B5="NV",C6,B5/Einstellungen!$B$53)</f>
-        <v>31.391641785502152</v>
+        <v>31.194075304362865</v>
       </c>
       <c r="D5" s="18">
         <f>IF(B5="NV",D6,B5/Einstellungen!$B$54)</f>
-        <v>1.5695820892751076</v>
+        <v>1.5597037652181434</v>
       </c>
       <c r="E5" s="6">
         <f>IF(B5="NV",E6,B5/Einstellungen!$B$55)</f>
-        <v>0.13079850743959229</v>
+        <v>0.12997531376817861</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -15604,19 +15637,19 @@
       </c>
       <c r="B6" s="18">
         <f>IF((Spezifikation!J3-(1*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(1*Spezifikation!M3)))</f>
-        <v>252.67171949272179</v>
+        <v>251.05411648560124</v>
       </c>
       <c r="C6" s="18">
         <f>IF(B6="NV",C7,B6/Einstellungen!$B$53)</f>
-        <v>31.583964936590224</v>
+        <v>31.381764560700155</v>
       </c>
       <c r="D6" s="18">
         <f>IF(B6="NV",D7,B6/Einstellungen!$B$54)</f>
-        <v>1.5791982468295112</v>
+        <v>1.5690882280350078</v>
       </c>
       <c r="E6" s="6">
         <f>IF(B6="NV",E7,B6/Einstellungen!$B$55)</f>
-        <v>0.13159985390245926</v>
+        <v>0.13075735233625066</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -15625,19 +15658,19 @@
       </c>
       <c r="B7" s="18">
         <f>IF((Spezifikation!J3-(0.84*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.84*Spezifikation!M3)))</f>
-        <v>253.55091104055296</v>
+        <v>251.9121245145717</v>
       </c>
       <c r="C7" s="18">
         <f>IF(B7="NV",C8,B7/Einstellungen!$B$53)</f>
-        <v>31.69386388006912</v>
+        <v>31.489015564321463</v>
       </c>
       <c r="D7" s="18">
         <f>IF(B7="NV",D8,B7/Einstellungen!$B$54)</f>
-        <v>1.5846931940034561</v>
+        <v>1.574450778216073</v>
       </c>
       <c r="E7" s="6">
         <f>IF(B7="NV",E8,B7/Einstellungen!$B$55)</f>
-        <v>0.13205776616695467</v>
+        <v>0.13120423151800609</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -15646,19 +15679,19 @@
       </c>
       <c r="B8" s="22">
         <f>IF((Spezifikation!J3-(0.67*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.67*Spezifikation!M3)))</f>
-        <v>254.48505206012359</v>
+        <v>252.8237580453528</v>
       </c>
       <c r="C8" s="22">
         <f>IF(B8="NV",C9,B8/Einstellungen!$B$53)</f>
-        <v>31.810631507515449</v>
+        <v>31.6029697556691</v>
       </c>
       <c r="D8" s="22">
         <f>IF(B8="NV",D9,B8/Einstellungen!$B$54)</f>
-        <v>1.5905315753757725</v>
+        <v>1.5801484877834551</v>
       </c>
       <c r="E8" s="22">
         <f>IF(B8="NV",E9,B8/Einstellungen!$B$55)</f>
-        <v>0.13254429794798103</v>
+        <v>0.13167904064862127</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -15667,19 +15700,19 @@
       </c>
       <c r="B9" s="18">
         <f>IF((Spezifikation!J3-(0.52*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.52*Spezifikation!M3)))</f>
-        <v>255.3092941362153</v>
+        <v>253.62814057251262</v>
       </c>
       <c r="C9" s="18">
         <f>IF(B9="NV",C10,B9/Einstellungen!$B$53)</f>
-        <v>31.913661767026912</v>
+        <v>31.703517571564078</v>
       </c>
       <c r="D9" s="18">
         <f>IF(B9="NV",D10,B9/Einstellungen!$B$54)</f>
-        <v>1.5956830883513455</v>
+        <v>1.585175878578204</v>
       </c>
       <c r="E9" s="6">
         <f>IF(B9="NV",E10,B9/Einstellungen!$B$55)</f>
-        <v>0.13297359069594547</v>
+        <v>0.132097989881517</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -15688,19 +15721,19 @@
       </c>
       <c r="B10" s="18">
         <f>IF((Spezifikation!J3-(0.25*Spezifikation!M3))&lt;0,"NV",(Spezifikation!J3-(0.25*Spezifikation!M3)))</f>
-        <v>256.79292987318041</v>
+        <v>255.07602912140027</v>
       </c>
       <c r="C10" s="18">
         <f>IF(B10="NV",C11,B10/Einstellungen!$B$53)</f>
-        <v>32.099116234147552</v>
+        <v>31.884503640175033</v>
       </c>
       <c r="D10" s="18">
         <f>IF(B10="NV",D11,B10/Einstellungen!$B$54)</f>
-        <v>1.6049558117073777</v>
+        <v>1.5942251820087516</v>
       </c>
       <c r="E10" s="6">
         <f>IF(B10="NV",E11,B10/Einstellungen!$B$55)</f>
-        <v>0.13374631764228145</v>
+        <v>0.13285209850072929</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -15709,19 +15742,19 @@
       </c>
       <c r="B11" s="22">
         <f>Spezifikation!J3</f>
-        <v>258.16666666666663</v>
+        <v>256.41666666666663</v>
       </c>
       <c r="C11" s="22">
         <f>B11/Einstellungen!B53</f>
-        <v>32.270833333333329</v>
+        <v>32.052083333333329</v>
       </c>
       <c r="D11" s="22">
         <f>B11/Einstellungen!B54</f>
-        <v>1.6135416666666664</v>
+        <v>1.6026041666666664</v>
       </c>
       <c r="E11" s="135">
         <f>B11/Einstellungen!B55</f>
-        <v>0.13446180555555554</v>
+        <v>0.1335503472222222</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -15730,19 +15763,19 @@
       </c>
       <c r="B12" s="18">
         <f>Spezifikation!J3+(0.25*Spezifikation!M3)</f>
-        <v>259.54040346015285</v>
+        <v>257.75730421193299</v>
       </c>
       <c r="C12" s="18">
         <f>B12/Einstellungen!B53</f>
-        <v>32.442550432519106</v>
+        <v>32.219663026491624</v>
       </c>
       <c r="D12" s="18">
         <f>B12/Einstellungen!B54</f>
-        <v>1.6221275216259552</v>
+        <v>1.6109831513245811</v>
       </c>
       <c r="E12" s="6">
         <f>B12/Einstellungen!B55</f>
-        <v>0.13517729346882962</v>
+        <v>0.1342485959437151</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -15751,19 +15784,19 @@
       </c>
       <c r="B13" s="18">
         <f>Spezifikation!J3+(0.52*Spezifikation!M3)</f>
-        <v>261.02403919711793</v>
+        <v>259.20519276082064</v>
       </c>
       <c r="C13" s="18">
         <f>B13/Einstellungen!B53</f>
-        <v>32.628004899639741</v>
+        <v>32.40064909510258</v>
       </c>
       <c r="D13" s="18">
         <f>B13/Einstellungen!B54</f>
-        <v>1.6314002449819871</v>
+        <v>1.620032454755129</v>
       </c>
       <c r="E13" s="6">
         <f>B13/Einstellungen!B55</f>
-        <v>0.1359500204151656</v>
+        <v>0.13500270456292743</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -15772,19 +15805,19 @@
       </c>
       <c r="B14" s="22">
         <f>Spezifikation!J3+(0.67*Spezifikation!M3)</f>
-        <v>261.84828127320969</v>
+        <v>260.00957528798045</v>
       </c>
       <c r="C14" s="22">
         <f>B14/Einstellungen!B53</f>
-        <v>32.731035159151212</v>
+        <v>32.501196910997557</v>
       </c>
       <c r="D14" s="22">
         <f>B14/Einstellungen!B54</f>
-        <v>1.6365517579575606</v>
+        <v>1.6250598455498779</v>
       </c>
       <c r="E14" s="135">
         <f>B14/Einstellungen!B55</f>
-        <v>0.13637931316313004</v>
+        <v>0.13542165379582316</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -15793,19 +15826,19 @@
       </c>
       <c r="B15" s="18">
         <f>Spezifikation!J3+(0.84*Spezifikation!M3)</f>
-        <v>262.78242229278032</v>
+        <v>260.92120881876156</v>
       </c>
       <c r="C15" s="18">
         <f>B15/Einstellungen!B53</f>
-        <v>32.847802786597541</v>
+        <v>32.615151102345195</v>
       </c>
       <c r="D15" s="18">
         <f>B15/Einstellungen!B54</f>
-        <v>1.642390139329877</v>
+        <v>1.6307575551172597</v>
       </c>
       <c r="E15" s="6">
         <f>B15/Einstellungen!B55</f>
-        <v>0.13686584494415641</v>
+        <v>0.13589646292643831</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -15814,19 +15847,19 @@
       </c>
       <c r="B16" s="18">
         <f>Spezifikation!J3+(1*Spezifikation!M3)</f>
-        <v>263.66161384061149</v>
+        <v>261.77921684773202</v>
       </c>
       <c r="C16" s="18">
         <f>B16/Einstellungen!B53</f>
-        <v>32.957701730076437</v>
+        <v>32.722402105966502</v>
       </c>
       <c r="D16" s="18">
         <f>B16/Einstellungen!B54</f>
-        <v>1.6478850865038219</v>
+        <v>1.6361201052983252</v>
       </c>
       <c r="E16" s="6">
         <f>B16/Einstellungen!B55</f>
-        <v>0.13732375720865181</v>
+        <v>0.13634334210819377</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -15835,19 +15868,19 @@
       </c>
       <c r="B17" s="18">
         <f>Spezifikation!J3+(1.28*Spezifikation!M3)</f>
-        <v>265.20019904931604</v>
+        <v>263.28073089843031</v>
       </c>
       <c r="C17" s="18">
         <f>B17/Einstellungen!B53</f>
-        <v>33.150024881164505</v>
+        <v>32.910091362303788</v>
       </c>
       <c r="D17" s="18">
         <f>B17/Einstellungen!B54</f>
-        <v>1.6575012440582253</v>
+        <v>1.6455045681151894</v>
       </c>
       <c r="E17" s="6">
         <f>B17/Einstellungen!B55</f>
-        <v>0.13812510367151878</v>
+        <v>0.13712538067626578</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -15856,19 +15889,19 @@
       </c>
       <c r="B18" s="26">
         <f>Spezifikation!J3+(2*Spezifikation!M3)</f>
-        <v>269.1565610145563</v>
+        <v>267.1417670287974</v>
       </c>
       <c r="C18" s="26">
         <f>B18/Einstellungen!B53</f>
-        <v>33.644570126819538</v>
+        <v>33.392720878599675</v>
       </c>
       <c r="D18" s="26">
         <f>B18/Einstellungen!B54</f>
-        <v>1.682228506340977</v>
+        <v>1.6696360439299838</v>
       </c>
       <c r="E18" s="136">
         <f>B18/Einstellungen!B55</f>
-        <v>0.14018570886174808</v>
+        <v>0.1391363369941653</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -16005,19 +16038,19 @@
       </c>
       <c r="C14" s="32">
         <f>Aufwandschätzung!B8</f>
-        <v>254.48505206012359</v>
+        <v>252.8237580453528</v>
       </c>
       <c r="D14" s="32">
         <f>Aufwandschätzung!B11</f>
-        <v>258.16666666666663</v>
+        <v>256.41666666666663</v>
       </c>
       <c r="E14" s="32">
         <f>Aufwandschätzung!B14</f>
-        <v>261.84828127320969</v>
+        <v>260.00957528798045</v>
       </c>
       <c r="F14" s="33">
         <f>Aufwandschätzung!B18</f>
-        <v>269.1565610145563</v>
+        <v>267.1417670287974</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -16026,19 +16059,19 @@
       </c>
       <c r="C15" s="34">
         <f>C14/C6</f>
-        <v>33.050006761055009</v>
+        <v>32.83425429160426</v>
       </c>
       <c r="D15" s="34">
         <f>D14/C6</f>
-        <v>33.52813852813852</v>
+        <v>33.300865800865793</v>
       </c>
       <c r="E15" s="34">
         <f>E14/C6</f>
-        <v>34.006270295222038</v>
+        <v>33.767477310127333</v>
       </c>
       <c r="F15" s="35">
         <f>F14/C6</f>
-        <v>34.955397534357964</v>
+        <v>34.693735977765897</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -16088,19 +16121,19 @@
       </c>
       <c r="C19" s="38">
         <f>(C5*C14)+C16+C17</f>
-        <v>35373.422236357183</v>
+        <v>35142.502368304042</v>
       </c>
       <c r="D19" s="38">
         <f>(C5*D14)+D16+D17</f>
-        <v>35885.166666666664</v>
+        <v>35641.916666666664</v>
       </c>
       <c r="E19" s="38">
         <f>(C5*E14)+E16+E17</f>
-        <v>36396.911096976146</v>
+        <v>36141.330965029279</v>
       </c>
       <c r="F19" s="40">
         <f>(C5*F14)+F16+F17</f>
-        <v>37412.761981023323</v>
+        <v>37132.705617002837</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -16962,18 +16995,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17155,14 +17188,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F155915-390F-4DB1-8323-6D9C71B4FD2C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90C8B9A1-CF49-4753-98D3-CDFF9713AD0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -17174,6 +17199,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F155915-390F-4DB1-8323-6D9C71B4FD2C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
